--- a/Financial Analysis/Models (Energy).xlsx
+++ b/Financial Analysis/Models (Energy).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDBCED4-EC35-4ADC-A049-E493C329A439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E9C45D-455B-4F85-A42A-54425CA48A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{14D7A11B-4B63-41BA-92AC-B31B19EF0AA6}"/>
   </bookViews>
@@ -31,42 +31,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Anton</author>
-  </authors>
-  <commentList>
-    <comment ref="U2" authorId="0" shapeId="0" xr:uid="{7CD827EB-527F-43CC-9DB0-AF57FEE9F23B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Anton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-analyse deeper with different regions and models</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Company</t>
   </si>
@@ -104,9 +70,6 @@
     <t>2028 E</t>
   </si>
   <si>
-    <t>2023 EV/E</t>
-  </si>
-  <si>
     <t>2024 EV/E</t>
   </si>
   <si>
@@ -122,21 +85,6 @@
     <t>2028 EV/E</t>
   </si>
   <si>
-    <t>2023 Rev</t>
-  </si>
-  <si>
-    <t>2022 RevG</t>
-  </si>
-  <si>
-    <t>2023 RevG</t>
-  </si>
-  <si>
-    <t>2023 GM%</t>
-  </si>
-  <si>
-    <t>2023 OM%</t>
-  </si>
-  <si>
     <t>Discount</t>
   </si>
   <si>
@@ -146,9 +94,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Segment</t>
-  </si>
-  <si>
     <t>Founded</t>
   </si>
   <si>
@@ -195,18 +140,43 @@
   </si>
   <si>
     <t>PLUG US</t>
+  </si>
+  <si>
+    <t>2025 Rev</t>
+  </si>
+  <si>
+    <t>2024 RevG</t>
+  </si>
+  <si>
+    <t>2025 RevG</t>
+  </si>
+  <si>
+    <t>2025 GM%</t>
+  </si>
+  <si>
+    <t>2025 OM%</t>
+  </si>
+  <si>
+    <t>2025 EV/B</t>
+  </si>
+  <si>
+    <t>2025 B/EV</t>
+  </si>
+  <si>
+    <t>ISBS Var</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="165" formatCode="0\x"/>
     <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,17 +219,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -283,7 +248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -321,9 +286,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -331,6 +293,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -363,32 +346,96 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>285.52</v>
-          </cell>
-          <cell r="F3">
-            <v>45571</v>
-          </cell>
-          <cell r="H3">
-            <v>45601</v>
+            <v>332.45</v>
+          </cell>
+          <cell r="E3">
+            <v>45909</v>
+          </cell>
+          <cell r="G3">
+            <v>45971</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>61015.623999999996</v>
+            <v>103857.37999999999</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-8157</v>
+            <v>-6249</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>69172.623999999996</v>
+            <v>110106.37999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="U3">
+            <v>25809.200000000001</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="S15">
+            <v>1588</v>
+          </cell>
+          <cell r="T15">
+            <v>3742</v>
+          </cell>
+          <cell r="U15">
+            <v>2203.3357160000005</v>
+          </cell>
+          <cell r="V15">
+            <v>3891.0411407519982</v>
+          </cell>
+          <cell r="W15">
+            <v>4232.0017609521583</v>
+          </cell>
+          <cell r="X15">
+            <v>4507.3319396302886</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="T19">
+            <v>-5.4177702865398469E-2</v>
+          </cell>
+          <cell r="U19">
+            <v>9.5095044127630812E-2</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="AH21">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="U22">
+            <v>0.18578801357655411</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="U23">
+            <v>0.12163589727694003</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AH27">
+            <v>-0.40653647602383658</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AH28" t="str">
+            <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="L42">
+            <v>53038</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -408,86 +455,91 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>24.61</v>
+            <v>70.709999999999994</v>
           </cell>
           <cell r="E3">
-            <v>45617</v>
+            <v>45927</v>
           </cell>
           <cell r="G3">
-            <v>45694</v>
+            <v>45960</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>5625.8459999999995</v>
+            <v>16546.14</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-989.69999999999993</v>
+            <v>-771.2</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>6615.5459999999994</v>
+            <v>17317.34</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="7">
-          <cell r="S7">
-            <v>1333.3</v>
+          <cell r="Y7">
+            <v>1751.5670000000002</v>
           </cell>
         </row>
         <row r="28">
-          <cell r="S28">
+          <cell r="W28">
             <v>-302.29999999999995</v>
           </cell>
-          <cell r="T28">
-            <v>-120.18044999999987</v>
-          </cell>
-          <cell r="U28">
-            <v>-63.599760827999852</v>
-          </cell>
-          <cell r="V28">
-            <v>-58.153296496200042</v>
-          </cell>
-          <cell r="W28">
-            <v>-32.414831841420252</v>
-          </cell>
           <cell r="X28">
-            <v>-11.955658830133736</v>
+            <v>-29.800000000000253</v>
+          </cell>
+          <cell r="Y28">
+            <v>43.17933000000022</v>
+          </cell>
+          <cell r="Z28">
+            <v>145.19444115000002</v>
+          </cell>
+          <cell r="AA28">
+            <v>188.6412343169998</v>
+          </cell>
+          <cell r="AB28">
+            <v>236.63731889367591</v>
           </cell>
         </row>
         <row r="34">
-          <cell r="AI34">
-            <v>0.1</v>
+          <cell r="AM34">
+            <v>0.09</v>
           </cell>
         </row>
         <row r="36">
-          <cell r="R36">
-            <v>0.23349105122402825</v>
-          </cell>
-          <cell r="S36">
-            <v>0.1118245496997996</v>
+          <cell r="X36">
+            <v>0.10537763444086101</v>
+          </cell>
+          <cell r="Y36">
+            <v>0.18846994164744224</v>
           </cell>
         </row>
         <row r="40">
-          <cell r="AI40">
-            <v>-1.1656162172133351</v>
+          <cell r="AM40">
+            <v>-0.83830827653230344</v>
           </cell>
         </row>
         <row r="41">
-          <cell r="S41">
-            <v>0.14805370134253365</v>
-          </cell>
-          <cell r="AI41" t="str">
+          <cell r="Y41">
+            <v>0.3176466158588282</v>
+          </cell>
+          <cell r="AM41" t="str">
             <v>Heavily overvalued</v>
           </cell>
         </row>
         <row r="45">
-          <cell r="S45">
-            <v>-0.15697892447311179</v>
+          <cell r="Y45">
+            <v>5.5310090907170664E-2</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="P83">
+            <v>2530.5</v>
           </cell>
         </row>
       </sheetData>
@@ -510,66 +562,96 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>11.19</v>
-          </cell>
-          <cell r="F3">
-            <v>45571</v>
-          </cell>
-          <cell r="H3">
-            <v>45623</v>
+            <v>2.37</v>
+          </cell>
+          <cell r="E3">
+            <v>45927</v>
+          </cell>
+          <cell r="G3">
+            <v>45972</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>1366.299</v>
+            <v>2736.8760000000002</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>294.60000000000002</v>
+            <v>506.29999999999973</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>1071.6990000000001</v>
+            <v>2230.5760000000005</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="6">
-          <cell r="M6"/>
-        </row>
-        <row r="17">
-          <cell r="M17"/>
-          <cell r="N17">
-            <v>-581.5</v>
-          </cell>
-          <cell r="O17">
-            <v>-111.6</v>
-          </cell>
-          <cell r="P17">
-            <v>-131.6</v>
-          </cell>
-          <cell r="Q17">
-            <v>4.3800000000000008</v>
-          </cell>
-          <cell r="R17">
-            <v>50.549999999999983</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="AC23">
-            <v>0.12</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="AC29">
-            <v>-0.8083382331398179</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AC30" t="str">
+        <row r="8">
+          <cell r="AA8">
+            <v>628.79999999999995</v>
+          </cell>
+          <cell r="AB8">
+            <v>738.56</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Z33">
+            <v>-1368.8</v>
+          </cell>
+          <cell r="AA33">
+            <v>-2104.9</v>
+          </cell>
+          <cell r="AB33">
+            <v>-910.35050000000001</v>
+          </cell>
+          <cell r="AC33">
+            <v>-508.71392100000014</v>
+          </cell>
+          <cell r="AD33">
+            <v>-351.38562542999983</v>
+          </cell>
+          <cell r="AE33">
+            <v>-191.72685569219993</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="AP39">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="AA42">
+            <v>-0.29443447037701986</v>
+          </cell>
+          <cell r="AB42">
+            <v>0.17455470737913492</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AP45">
+            <v>-0.84446381726903419</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="AP46" t="str">
             <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="AB48">
+            <v>-0.44518996425476615</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="AB51">
+            <v>-1.0778413399046796</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="P93">
+            <v>3353.8</v>
           </cell>
         </row>
       </sheetData>
@@ -592,81 +674,62 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>4.95</v>
+            <v>109.4</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45927</v>
           </cell>
           <cell r="G3">
-            <v>45817</v>
+            <v>45623</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>104.44500000000001</v>
+            <v>16147.44</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>128</v>
+            <v>683</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>-23.554999999999993</v>
+            <v>15464.44</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="17">
+          <cell r="R17">
+            <v>-73.699999999999989</v>
+          </cell>
+          <cell r="S17">
+            <v>-111.6</v>
+          </cell>
+          <cell r="T17">
+            <v>-131.6</v>
+          </cell>
+          <cell r="U17">
+            <v>-92.82</v>
+          </cell>
+          <cell r="V17">
+            <v>-33.285000000000011</v>
+          </cell>
+        </row>
         <row r="23">
-          <cell r="Y23">
-            <v>45.7</v>
-          </cell>
-          <cell r="Z23">
-            <v>31.400000000000002</v>
-          </cell>
-          <cell r="AA23">
-            <v>49.3</v>
-          </cell>
-          <cell r="AB23">
-            <v>114.3</v>
-          </cell>
-          <cell r="AC23">
-            <v>125.6</v>
-          </cell>
-          <cell r="AD23">
-            <v>122.6</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="X31">
-            <v>-50.70000000000001</v>
-          </cell>
-          <cell r="Y31">
-            <v>-77.599999999999994</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="AS42">
-            <v>0.12</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="AS48">
-            <v>0.25873266742717416</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="AC49">
-            <v>-8.5899513776336936E-2</v>
-          </cell>
-          <cell r="AS49" t="str">
-            <v>Slightly undervalued</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="AC52">
-            <v>-1.1037277147487841</v>
+          <cell r="AG23">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AG29">
+            <v>-0.83979249526057242</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AG30" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -689,88 +752,91 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>1.21</v>
+            <v>7.85</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45927</v>
           </cell>
           <cell r="G3">
-            <v>45785</v>
+            <v>45912</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>1119.492</v>
+            <v>191.54</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>361</v>
+            <v>100.89999999999998</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>758.49199999999996</v>
+            <v>90.640000000000015</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="8">
-          <cell r="Z8">
-            <v>891.2</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="Z33">
-            <v>-1368.8</v>
-          </cell>
-          <cell r="AA33">
-            <v>-2104.9</v>
-          </cell>
-          <cell r="AB33">
-            <v>-722.21355000000028</v>
-          </cell>
-          <cell r="AC33">
-            <v>-504.726876</v>
-          </cell>
-          <cell r="AD33">
-            <v>-298.75576328999978</v>
-          </cell>
-          <cell r="AE33">
-            <v>-107.28387832140008</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="AP39">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="Y42">
-            <v>0.3960987261146498</v>
-          </cell>
-          <cell r="Z42">
-            <v>0.27060165383518697</v>
+        <row r="13">
+          <cell r="AE13">
+            <v>160.12</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24">
+            <v>45.7</v>
+          </cell>
+          <cell r="Z24">
+            <v>31.400000000000002</v>
+          </cell>
+          <cell r="AA24">
+            <v>49.3</v>
+          </cell>
+          <cell r="AB24">
+            <v>114.3</v>
+          </cell>
+          <cell r="AC24">
+            <v>125.6</v>
+          </cell>
+          <cell r="AD24">
+            <v>122.6</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="AS43">
+            <v>0.12</v>
           </cell>
         </row>
         <row r="45">
-          <cell r="AP45">
-            <v>-0.26355921079086486</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="AP46" t="str">
-            <v>Slightly overvalued</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="Z48">
-            <v>-0.56979353680430866</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="Z51">
-            <v>-1.5075179533213643</v>
+          <cell r="AD45">
+            <v>-9.0761750405186525E-2</v>
+          </cell>
+          <cell r="AE45">
+            <v>0.4270944741532976</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="AS49">
+            <v>-0.99110072258398429</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="AE50">
+            <v>-0.15485885585810655</v>
+          </cell>
+          <cell r="AS50" t="str">
+            <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="AE53">
+            <v>-1.2246814888833375</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="AE85">
+            <v>830.6</v>
           </cell>
         </row>
       </sheetData>
@@ -1075,8 +1141,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F50123-7912-4358-B5CC-BC69536C3F1F}">
-  <dimension ref="B2:AF9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F50123-7912-4358-B5CC-BC69536C3F1F}">
+  <dimension ref="B2:AG9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
@@ -1087,19 +1153,19 @@
     <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.109375" customWidth="1"/>
-    <col min="28" max="28" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="9.5546875" customWidth="1"/>
+    <col min="22" max="22" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.109375" customWidth="1"/>
+    <col min="30" max="30" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1152,49 +1218,52 @@
         <v>16</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="AB2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1207,573 +1276,685 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="6" t="e">
-        <f t="shared" ref="N3:S3" si="0">TRIMMEAN(N6:N1048576,80%)</f>
-        <v>#DIV/0!</v>
+      <c r="N3" s="6">
+        <f>TRIMMEAN(N4:N1048576,80%)</f>
+        <v>-1.0597063993538887</v>
       </c>
       <c r="O3" s="6">
-        <f t="shared" si="0"/>
-        <v>-0.7501592356687895</v>
+        <f t="shared" ref="O3:R3" si="0">TRIMMEAN(O4:O1048576,80%)</f>
+        <v>1.838539553752536</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>-1.0502323031740399</v>
+        <v>0.79300087489063886</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>-1.5027771178168843</v>
+        <v>0.72165605095541419</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>-0.1875398089171974</v>
-      </c>
-      <c r="S3" s="6">
-        <f t="shared" si="0"/>
-        <v>-0.19212887438825443</v>
-      </c>
-      <c r="T3" s="7"/>
-      <c r="U3" s="8">
-        <f t="shared" ref="U3:Y3" si="1">TRIMMEAN(U6:U1048576,80%)</f>
+        <v>0.73931484502446998</v>
+      </c>
+      <c r="S3" s="24">
+        <f>TRIMMEAN(S4:S1048576,80%)</f>
+        <v>1.3705397872823148</v>
+      </c>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="8">
+        <f>TRIMMEAN(W4:W1048576,80%)</f>
+        <v>-5.4177702865398469E-2</v>
+      </c>
+      <c r="X3" s="8">
+        <f>TRIMMEAN(X4:X1048576,80%)</f>
+        <v>0.17455470737913492</v>
+      </c>
+      <c r="Y3" s="8">
+        <f>TRIMMEAN(Y4:Y1048576,80%)</f>
         <v>0</v>
-      </c>
-      <c r="V3" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W3" s="8">
-        <f t="shared" si="1"/>
-        <v>-8.5899513776336936E-2</v>
-      </c>
-      <c r="X3" s="8">
-        <f t="shared" si="1"/>
-        <v>-1.1037277147487841</v>
-      </c>
-      <c r="Y3" s="8">
-        <f t="shared" si="1"/>
-        <v>0.12</v>
       </c>
       <c r="Z3" s="8">
         <f>TRIMMEAN(Z4:Z1048576,80%)</f>
-        <v>-0.53594872196534138</v>
-      </c>
-      <c r="AA3" s="9" t="e">
-        <f>INDEX(AA6:AA53,MODE(MATCH(AA6:AA53,AA6:AA53,0)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="8">
+        <f>TRIMMEAN(AA4:AA1048576,80%)</f>
+        <v>0.09</v>
+      </c>
+      <c r="AB3" s="8">
+        <f>TRIMMEAN(AB4:AB1048576,80%)</f>
+        <v>-0.83979249526057242</v>
+      </c>
+      <c r="AC3" s="9" t="str">
+        <f>INDEX(AC4:AC8,MODE(MATCH(AC4:AC8,AC4:AC8,0)))</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AD3" s="10"/>
     </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D4" s="12">
         <f>[1]Main!$D$3</f>
-        <v>285.52</v>
+        <v>332.45</v>
       </c>
       <c r="E4" s="13">
         <f>[1]Main!$D$5</f>
-        <v>61015.623999999996</v>
+        <v>103857.37999999999</v>
       </c>
       <c r="F4" s="13">
         <f>[1]Main!$D$8</f>
-        <v>-8157</v>
+        <v>-6249</v>
       </c>
       <c r="G4" s="13">
         <f>[1]Main!$D$9</f>
-        <v>69172.623999999996</v>
-      </c>
-      <c r="AE4" s="18">
-        <f>[1]Main!$F$3</f>
-        <v>45571</v>
-      </c>
-      <c r="AF4" s="18">
-        <f>[1]Main!$H$3</f>
-        <v>45601</v>
+        <v>110106.37999999999</v>
+      </c>
+      <c r="H4" s="13">
+        <f>[1]Model!S$15</f>
+        <v>1588</v>
+      </c>
+      <c r="I4" s="13">
+        <f>[1]Model!T$15</f>
+        <v>3742</v>
+      </c>
+      <c r="J4" s="13">
+        <f>[1]Model!U$15</f>
+        <v>2203.3357160000005</v>
+      </c>
+      <c r="K4" s="13">
+        <f>[1]Model!V$15</f>
+        <v>3891.0411407519982</v>
+      </c>
+      <c r="L4" s="13">
+        <f>[1]Model!W$15</f>
+        <v>4232.0017609521583</v>
+      </c>
+      <c r="M4" s="13">
+        <f>[1]Model!X$15</f>
+        <v>4507.3319396302886</v>
+      </c>
+      <c r="N4" s="14">
+        <f>$G4/I4</f>
+        <v>29.424473543559593</v>
+      </c>
+      <c r="O4" s="14">
+        <f t="shared" ref="O4" si="1">$G4/J4</f>
+        <v>49.972584386681802</v>
+      </c>
+      <c r="P4" s="14">
+        <f t="shared" ref="P4" si="2">$G4/K4</f>
+        <v>28.297408332907111</v>
+      </c>
+      <c r="Q4" s="14">
+        <f t="shared" ref="Q4" si="3">$G4/L4</f>
+        <v>26.017564788353763</v>
+      </c>
+      <c r="R4" s="14">
+        <f t="shared" ref="R4" si="4">$G4/M4</f>
+        <v>24.428282956464795</v>
+      </c>
+      <c r="S4" s="23">
+        <f>G4/[1]Model!$L$42</f>
+        <v>2.0759904219616123</v>
+      </c>
+      <c r="T4" s="15">
+        <f>[1]Model!$L$42/G4-1</f>
+        <v>-0.51830220919078429</v>
+      </c>
+      <c r="U4" s="15">
+        <f>AVERAGE(T4,AB4)</f>
+        <v>-0.46241934260731044</v>
+      </c>
+      <c r="V4" s="13">
+        <f>[1]Model!$U$3</f>
+        <v>25809.200000000001</v>
+      </c>
+      <c r="W4" s="15">
+        <f>[1]Model!T$19</f>
+        <v>-5.4177702865398469E-2</v>
+      </c>
+      <c r="X4" s="15">
+        <f>[1]Model!U$19</f>
+        <v>9.5095044127630812E-2</v>
+      </c>
+      <c r="Y4" s="15">
+        <f>[1]Model!$U$22</f>
+        <v>0.18578801357655411</v>
+      </c>
+      <c r="Z4" s="15">
+        <f>[1]Model!$U$23</f>
+        <v>0.12163589727694003</v>
+      </c>
+      <c r="AA4" s="15">
+        <f>[1]Model!$AH$21</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AB4" s="15">
+        <f>[1]Model!$AH$27</f>
+        <v>-0.40653647602383658</v>
+      </c>
+      <c r="AC4" s="10" t="str">
+        <f>[1]Model!$AH$28</f>
+        <v>Overvalued</v>
+      </c>
+      <c r="AD4" s="10">
+        <v>1999</v>
+      </c>
+      <c r="AF4" s="17">
+        <f>[1]Main!$E$3</f>
+        <v>45909</v>
+      </c>
+      <c r="AG4" s="17">
+        <f>[1]Main!$G$3</f>
+        <v>45971</v>
       </c>
     </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D5" s="12">
         <f>[2]Main!$D$3</f>
-        <v>24.61</v>
+        <v>70.709999999999994</v>
       </c>
       <c r="E5" s="13">
         <f>[2]Main!$D$5</f>
-        <v>5625.8459999999995</v>
+        <v>16546.14</v>
       </c>
       <c r="F5" s="13">
         <f>[2]Main!$D$8</f>
-        <v>-989.69999999999993</v>
+        <v>-771.2</v>
       </c>
       <c r="G5" s="13">
         <f>[2]Main!$D$9</f>
-        <v>6615.5459999999994</v>
+        <v>17317.34</v>
       </c>
       <c r="H5" s="13">
-        <f>[2]Model!S$28</f>
+        <f>[2]Model!W$28</f>
         <v>-302.29999999999995</v>
       </c>
       <c r="I5" s="13">
-        <f>[2]Model!T$28</f>
-        <v>-120.18044999999987</v>
+        <f>[2]Model!X$28</f>
+        <v>-29.800000000000253</v>
       </c>
       <c r="J5" s="13">
-        <f>[2]Model!U$28</f>
-        <v>-63.599760827999852</v>
+        <f>[2]Model!Y$28</f>
+        <v>43.17933000000022</v>
       </c>
       <c r="K5" s="13">
-        <f>[2]Model!V$28</f>
-        <v>-58.153296496200042</v>
+        <f>[2]Model!Z$28</f>
+        <v>145.19444115000002</v>
       </c>
       <c r="L5" s="13">
-        <f>[2]Model!W$28</f>
-        <v>-32.414831841420252</v>
+        <f>[2]Model!AA$28</f>
+        <v>188.6412343169998</v>
       </c>
       <c r="M5" s="13">
-        <f>[2]Model!X$28</f>
-        <v>-11.955658830133736</v>
+        <f>[2]Model!AB$28</f>
+        <v>236.63731889367591</v>
       </c>
       <c r="N5" s="14">
-        <f t="shared" ref="N5:S5" si="2">$G5/H5</f>
-        <v>-21.884042342044328</v>
+        <f>$G5/I5</f>
+        <v>-581.11879194630376</v>
       </c>
       <c r="O5" s="14">
-        <f t="shared" si="2"/>
-        <v>-55.046773414478032</v>
+        <f>$G5/J5</f>
+        <v>401.05624612516942</v>
       </c>
       <c r="P5" s="14">
-        <f t="shared" si="2"/>
-        <v>-104.01841003602485</v>
+        <f>$G5/K5</f>
+        <v>119.26999314050528</v>
       </c>
       <c r="Q5" s="14">
-        <f t="shared" si="2"/>
-        <v>-113.76046412832821</v>
+        <f>$G5/L5</f>
+        <v>91.800395935171267</v>
       </c>
       <c r="R5" s="14">
-        <f t="shared" si="2"/>
-        <v>-204.09009160882138</v>
-      </c>
-      <c r="S5" s="14">
-        <f t="shared" si="2"/>
-        <v>-553.34014578316624</v>
-      </c>
-      <c r="T5" s="13">
-        <f>[2]Model!$S$7</f>
-        <v>1333.3</v>
-      </c>
-      <c r="U5" s="16">
-        <f>[2]Model!$R$36</f>
-        <v>0.23349105122402825</v>
-      </c>
-      <c r="V5" s="16">
-        <f>[2]Model!$S$36</f>
-        <v>0.1118245496997996</v>
-      </c>
-      <c r="W5" s="16">
-        <f>[2]Model!$S$41</f>
-        <v>0.14805370134253365</v>
-      </c>
-      <c r="X5" s="16">
-        <f>[2]Model!$S$45</f>
-        <v>-0.15697892447311179</v>
-      </c>
-      <c r="Y5" s="16">
-        <f>[2]Model!$AI$34</f>
+        <f>$G5/M5</f>
+        <v>73.18093393282949</v>
+      </c>
+      <c r="S5" s="23">
+        <f>G5/[2]Model!$P$83</f>
+        <v>6.8434459592965817</v>
+      </c>
+      <c r="T5" s="15">
+        <f>[2]Model!$P$83/G5-1</f>
+        <v>-0.8538747867744122</v>
+      </c>
+      <c r="U5" s="15">
+        <f>AVERAGE(T5,AB5)</f>
+        <v>-0.84609153165335782</v>
+      </c>
+      <c r="V5" s="20">
+        <f>[2]Model!$Y$7</f>
+        <v>1751.5670000000002</v>
+      </c>
+      <c r="W5" s="21">
+        <f>[2]Model!X$36</f>
+        <v>0.10537763444086101</v>
+      </c>
+      <c r="X5" s="21">
+        <f>[2]Model!Y$36</f>
+        <v>0.18846994164744224</v>
+      </c>
+      <c r="Y5" s="21">
+        <f>[2]Model!$Y$41</f>
+        <v>0.3176466158588282</v>
+      </c>
+      <c r="Z5" s="21">
+        <f>[2]Model!$Y$45</f>
+        <v>5.5310090907170664E-2</v>
+      </c>
+      <c r="AA5" s="15">
+        <f>[2]Model!$AM$34</f>
+        <v>0.09</v>
+      </c>
+      <c r="AB5" s="15">
+        <f>[2]Model!$AM$40</f>
+        <v>-0.83830827653230344</v>
+      </c>
+      <c r="AC5" s="10" t="str">
+        <f>[2]Model!$AM$41</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>2001</v>
+      </c>
+      <c r="AF5" s="17">
+        <f>[2]Main!$E$3</f>
+        <v>45927</v>
+      </c>
+      <c r="AG5" s="17">
+        <f>[2]Main!$G$3</f>
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="12">
+        <f>[4]Main!$D$3</f>
+        <v>109.4</v>
+      </c>
+      <c r="E6" s="13">
+        <f>[4]Main!$D$5</f>
+        <v>16147.44</v>
+      </c>
+      <c r="F6" s="13">
+        <f>[4]Main!$D$8</f>
+        <v>683</v>
+      </c>
+      <c r="G6" s="13">
+        <f>[4]Main!$D$9</f>
+        <v>15464.44</v>
+      </c>
+      <c r="H6" s="13">
+        <f>[4]Model!Q$17</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="13">
+        <f>[4]Model!R$17</f>
+        <v>-73.699999999999989</v>
+      </c>
+      <c r="J6" s="13">
+        <f>[4]Model!S$17</f>
+        <v>-111.6</v>
+      </c>
+      <c r="K6" s="13">
+        <f>[4]Model!T$17</f>
+        <v>-131.6</v>
+      </c>
+      <c r="L6" s="13">
+        <f>[4]Model!U$17</f>
+        <v>-92.82</v>
+      </c>
+      <c r="M6" s="13">
+        <f>[4]Model!V$17</f>
+        <v>-33.285000000000011</v>
+      </c>
+      <c r="N6" s="14">
+        <f>$G6/I6</f>
+        <v>-209.82957937584808</v>
+      </c>
+      <c r="O6" s="14">
+        <f>$G6/J6</f>
+        <v>-138.57025089605736</v>
+      </c>
+      <c r="P6" s="14">
+        <f>$G6/K6</f>
+        <v>-117.51094224924013</v>
+      </c>
+      <c r="Q6" s="14">
+        <f>$G6/L6</f>
+        <v>-166.6067657832364</v>
+      </c>
+      <c r="R6" s="14">
+        <f>$G6/M6</f>
+        <v>-464.606879975965</v>
+      </c>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="18">
+        <f>[4]Model!$Q$6</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="19">
+        <f>[4]Model!$P$22</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="19">
+        <f>[4]Model!$Q$22</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="19">
+        <f>[4]Model!$Q$23</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="19">
+        <f>[4]Model!$Q$26</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="15">
+        <f>[4]Model!$AG$23</f>
+        <v>0.09</v>
+      </c>
+      <c r="AB6" s="15">
+        <f>[4]Model!$AG$29</f>
+        <v>-0.83979249526057242</v>
+      </c>
+      <c r="AC6" s="15" t="str">
+        <f>[4]Model!$AG$30</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AD6" s="10">
+        <v>2013</v>
+      </c>
+      <c r="AF6" s="16">
+        <f>[4]Main!$E$3</f>
+        <v>45927</v>
+      </c>
+      <c r="AG6" s="16">
+        <f>[4]Main!$G$3</f>
+        <v>45623</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="12">
+        <f>[3]Main!$D$3</f>
+        <v>2.37</v>
+      </c>
+      <c r="E7" s="13">
+        <f>[3]Main!$D$5</f>
+        <v>2736.8760000000002</v>
+      </c>
+      <c r="F7" s="13">
+        <f>[3]Main!$D$8</f>
+        <v>506.29999999999973</v>
+      </c>
+      <c r="G7" s="13">
+        <f>[3]Main!$D$9</f>
+        <v>2230.5760000000005</v>
+      </c>
+      <c r="H7" s="13">
+        <f>[3]Model!Z$33</f>
+        <v>-1368.8</v>
+      </c>
+      <c r="I7" s="13">
+        <f>[3]Model!AA$33</f>
+        <v>-2104.9</v>
+      </c>
+      <c r="J7" s="13">
+        <f>[3]Model!AB$33</f>
+        <v>-910.35050000000001</v>
+      </c>
+      <c r="K7" s="13">
+        <f>[3]Model!AC$33</f>
+        <v>-508.71392100000014</v>
+      </c>
+      <c r="L7" s="13">
+        <f>[3]Model!AD$33</f>
+        <v>-351.38562542999983</v>
+      </c>
+      <c r="M7" s="13">
+        <f>[3]Model!AE$33</f>
+        <v>-191.72685569219993</v>
+      </c>
+      <c r="N7" s="14">
+        <f>$G7/I7</f>
+        <v>-1.0597063993538887</v>
+      </c>
+      <c r="O7" s="14">
+        <f>$G7/J7</f>
+        <v>-2.4502386718082767</v>
+      </c>
+      <c r="P7" s="14">
+        <f>$G7/K7</f>
+        <v>-4.3847355221088984</v>
+      </c>
+      <c r="Q7" s="14">
+        <f>$G7/L7</f>
+        <v>-6.3479432241156308</v>
+      </c>
+      <c r="R7" s="14">
+        <f>$G7/M7</f>
+        <v>-11.634134362381594</v>
+      </c>
+      <c r="S7" s="23">
+        <f>G7/[3]Model!$P$93</f>
+        <v>0.6650891526030176</v>
+      </c>
+      <c r="T7" s="15">
+        <f>[3]Model!$P$93/G7-1</f>
+        <v>0.50355782542267091</v>
+      </c>
+      <c r="U7" s="15">
+        <f t="shared" ref="U7:U8" si="5">AVERAGE(T7,AB7)</f>
+        <v>-0.17045299592318164</v>
+      </c>
+      <c r="V7" s="20">
+        <f>[3]Model!$AB$8</f>
+        <v>738.56</v>
+      </c>
+      <c r="W7" s="21">
+        <f>[3]Model!AA$42</f>
+        <v>-0.29443447037701986</v>
+      </c>
+      <c r="X7" s="21">
+        <f>[3]Model!AB$42</f>
+        <v>0.17455470737913492</v>
+      </c>
+      <c r="Y7" s="21">
+        <f>[3]Model!$AB$48</f>
+        <v>-0.44518996425476615</v>
+      </c>
+      <c r="Z7" s="21">
+        <f>[3]Model!$AB$51</f>
+        <v>-1.0778413399046796</v>
+      </c>
+      <c r="AA7" s="15">
+        <f>[3]Model!$AP$39</f>
         <v>0.1</v>
       </c>
-      <c r="Z5" s="16">
-        <f>[2]Model!$AI$40</f>
-        <v>-1.1656162172133351</v>
-      </c>
-      <c r="AA5" s="10" t="str">
-        <f>[2]Model!$AI$41</f>
+      <c r="AB7" s="15">
+        <f>[3]Model!$AP$45</f>
+        <v>-0.84446381726903419</v>
+      </c>
+      <c r="AC7" s="10" t="str">
+        <f>[3]Model!$AP$46</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AC5" s="10">
-        <v>2001</v>
-      </c>
-      <c r="AE5" s="18">
-        <f>[2]Main!$E$3</f>
-        <v>45617</v>
-      </c>
-      <c r="AF5" s="18">
-        <f>[2]Main!$G$3</f>
-        <v>45694</v>
+      <c r="AD7" s="10">
+        <v>1997</v>
+      </c>
+      <c r="AF7" s="17">
+        <f>[3]Main!$E$3</f>
+        <v>45927</v>
+      </c>
+      <c r="AG7" s="17">
+        <f>[3]Main!$G$3</f>
+        <v>45972</v>
       </c>
     </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="12">
-        <f>[3]Main!$D$3</f>
-        <v>11.19</v>
-      </c>
-      <c r="E6" s="13">
-        <f>[3]Main!$D$5</f>
-        <v>1366.299</v>
-      </c>
-      <c r="F6" s="13">
-        <f>[3]Main!$D$8</f>
-        <v>294.60000000000002</v>
-      </c>
-      <c r="G6" s="13">
-        <f>[3]Main!$D$9</f>
-        <v>1071.6990000000001</v>
-      </c>
-      <c r="H6" s="13">
-        <f>[3]Model!M$17</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="13">
-        <f>[3]Model!N$17</f>
-        <v>-581.5</v>
-      </c>
-      <c r="J6" s="13">
-        <f>[3]Model!O$17</f>
-        <v>-111.6</v>
-      </c>
-      <c r="K6" s="13">
-        <f>[3]Model!P$17</f>
-        <v>-131.6</v>
-      </c>
-      <c r="L6" s="13">
-        <f>[3]Model!Q$17</f>
-        <v>4.3800000000000008</v>
-      </c>
-      <c r="M6" s="13">
-        <f>[3]Model!R$17</f>
-        <v>50.549999999999983</v>
-      </c>
-      <c r="N6" s="14" t="e">
-        <f t="shared" ref="N6:S6" si="3">$G6/H6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O6" s="14">
-        <f t="shared" si="3"/>
-        <v>-1.8429905417024937</v>
-      </c>
-      <c r="P6" s="14">
-        <f t="shared" si="3"/>
-        <v>-9.6030376344086026</v>
-      </c>
-      <c r="Q6" s="14">
-        <f t="shared" si="3"/>
-        <v>-8.1436094224924016</v>
-      </c>
-      <c r="R6" s="14">
-        <f t="shared" si="3"/>
-        <v>244.68013698630133</v>
-      </c>
-      <c r="S6" s="14">
-        <f t="shared" si="3"/>
-        <v>21.200771513353125</v>
-      </c>
-      <c r="T6" s="15">
-        <f>[3]Model!$M$6</f>
-        <v>0</v>
-      </c>
-      <c r="U6" s="16">
-        <f>[3]Model!$L$22</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="16">
-        <f>[3]Model!$M$22</f>
-        <v>0</v>
-      </c>
-      <c r="W6" s="16">
-        <f>[3]Model!$M$23</f>
-        <v>0</v>
-      </c>
-      <c r="X6" s="16">
-        <f>[3]Model!$M$26</f>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="16">
-        <f>[3]Model!$AC$23</f>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="12">
+        <f>[5]Main!$D$3</f>
+        <v>7.85</v>
+      </c>
+      <c r="E8" s="13">
+        <f>[5]Main!$D$5</f>
+        <v>191.54</v>
+      </c>
+      <c r="F8" s="13">
+        <f>[5]Main!$D$8</f>
+        <v>100.89999999999998</v>
+      </c>
+      <c r="G8" s="13">
+        <f>[5]Main!$D$9</f>
+        <v>90.640000000000015</v>
+      </c>
+      <c r="H8" s="13">
+        <f>[5]Model!Y$24</f>
+        <v>45.7</v>
+      </c>
+      <c r="I8" s="13">
+        <f>[5]Model!Z$24</f>
+        <v>31.400000000000002</v>
+      </c>
+      <c r="J8" s="13">
+        <f>[5]Model!AA$24</f>
+        <v>49.3</v>
+      </c>
+      <c r="K8" s="13">
+        <f>[5]Model!AB$24</f>
+        <v>114.3</v>
+      </c>
+      <c r="L8" s="13">
+        <f>[5]Model!AC$24</f>
+        <v>125.6</v>
+      </c>
+      <c r="M8" s="13">
+        <f>[5]Model!AD$24</f>
+        <v>122.6</v>
+      </c>
+      <c r="N8" s="14">
+        <f t="shared" ref="N8" si="6">$G8/I8</f>
+        <v>2.8866242038216563</v>
+      </c>
+      <c r="O8" s="14">
+        <f t="shared" ref="O8" si="7">$G8/J8</f>
+        <v>1.838539553752536</v>
+      </c>
+      <c r="P8" s="14">
+        <f t="shared" ref="P8" si="8">$G8/K8</f>
+        <v>0.79300087489063886</v>
+      </c>
+      <c r="Q8" s="14">
+        <f t="shared" ref="Q8" si="9">$G8/L8</f>
+        <v>0.72165605095541419</v>
+      </c>
+      <c r="R8" s="14">
+        <f t="shared" ref="R8" si="10">$G8/M8</f>
+        <v>0.73931484502446998</v>
+      </c>
+      <c r="S8" s="23">
+        <f>G8/[5]Model!$AE$85</f>
+        <v>0.10912593306043825</v>
+      </c>
+      <c r="T8" s="15">
+        <f>[5]Model!$AE$85/G8-1</f>
+        <v>8.1637246248896727</v>
+      </c>
+      <c r="U8" s="15">
+        <f t="shared" si="5"/>
+        <v>3.5863119511528443</v>
+      </c>
+      <c r="V8" s="22">
+        <f>[5]Model!$AE$13</f>
+        <v>160.12</v>
+      </c>
+      <c r="W8" s="21">
+        <f>[5]Model!$AD$45</f>
+        <v>-9.0761750405186525E-2</v>
+      </c>
+      <c r="X8" s="21">
+        <f>[5]Model!$AE$45</f>
+        <v>0.4270944741532976</v>
+      </c>
+      <c r="Y8" s="21">
+        <f>[5]Model!$AE$50</f>
+        <v>-0.15485885585810655</v>
+      </c>
+      <c r="Z8" s="21">
+        <f>[5]Model!$AE$53</f>
+        <v>-1.2246814888833375</v>
+      </c>
+      <c r="AA8" s="15">
+        <f>[5]Model!$AS$43</f>
         <v>0.12</v>
       </c>
-      <c r="Z6" s="16">
-        <f>[3]Model!$AC$29</f>
-        <v>-0.8083382331398179</v>
-      </c>
-      <c r="AA6" s="16" t="str">
-        <f>[3]Model!$AC$30</f>
-        <v>Heavily overvalued</v>
-      </c>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="10">
-        <v>2013</v>
-      </c>
-      <c r="AE6" s="17">
-        <f>[3]Main!$F$3</f>
-        <v>45571</v>
-      </c>
-      <c r="AF6" s="17">
-        <f>[3]Main!$H$3</f>
-        <v>45623</v>
+      <c r="AB8" s="15">
+        <f>[5]Model!$AS$49</f>
+        <v>-0.99110072258398429</v>
+      </c>
+      <c r="AC8" s="10" t="str">
+        <f>[5]Model!$AS$50</f>
+        <v>Overvalued</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>1969</v>
+      </c>
+      <c r="AF8" s="16">
+        <f>[5]Main!$E$3</f>
+        <v>45927</v>
+      </c>
+      <c r="AG8" s="16">
+        <f>[5]Main!$G$3</f>
+        <v>45912</v>
       </c>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="12">
-        <f>[4]Main!$D$3</f>
-        <v>4.95</v>
-      </c>
-      <c r="E7" s="13">
-        <f>[4]Main!$D$5</f>
-        <v>104.44500000000001</v>
-      </c>
-      <c r="F7" s="13">
-        <f>[4]Main!$D$8</f>
-        <v>128</v>
-      </c>
-      <c r="G7" s="13">
-        <f>[4]Main!$D$9</f>
-        <v>-23.554999999999993</v>
-      </c>
-      <c r="H7" s="13">
-        <f>[4]Model!Y$23</f>
-        <v>45.7</v>
-      </c>
-      <c r="I7" s="13">
-        <f>[4]Model!Z$23</f>
-        <v>31.400000000000002</v>
-      </c>
-      <c r="J7" s="13">
-        <f>[4]Model!AA$23</f>
-        <v>49.3</v>
-      </c>
-      <c r="K7" s="13">
-        <f>[4]Model!AB$23</f>
-        <v>114.3</v>
-      </c>
-      <c r="L7" s="13">
-        <f>[4]Model!AC$23</f>
-        <v>125.6</v>
-      </c>
-      <c r="M7" s="13">
-        <f>[4]Model!AD$23</f>
-        <v>122.6</v>
-      </c>
-      <c r="N7" s="14">
-        <f t="shared" ref="N7" si="4">$G7/H7</f>
-        <v>-0.5154266958424506</v>
-      </c>
-      <c r="O7" s="14">
-        <f t="shared" ref="O7" si="5">$G7/I7</f>
-        <v>-0.7501592356687895</v>
-      </c>
-      <c r="P7" s="14">
-        <f t="shared" ref="P7" si="6">$G7/J7</f>
-        <v>-0.47778904665314387</v>
-      </c>
-      <c r="Q7" s="14">
-        <f t="shared" ref="Q7" si="7">$G7/K7</f>
-        <v>-0.20608048993875761</v>
-      </c>
-      <c r="R7" s="14">
-        <f t="shared" ref="R7" si="8">$G7/L7</f>
-        <v>-0.1875398089171974</v>
-      </c>
-      <c r="S7" s="14">
-        <f t="shared" ref="S7" si="9">$G7/M7</f>
-        <v>-0.19212887438825443</v>
-      </c>
-      <c r="T7" s="15">
-        <f>[4]Model!$Y$7</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="16">
-        <f>[4]Model!$X$31</f>
-        <v>-50.70000000000001</v>
-      </c>
-      <c r="V7" s="16">
-        <f>[4]Model!$Y$31</f>
-        <v>-77.599999999999994</v>
-      </c>
-      <c r="W7" s="16">
-        <f>[4]Model!$AC$49</f>
-        <v>-8.5899513776336936E-2</v>
-      </c>
-      <c r="X7" s="16">
-        <f>[4]Model!$AC$52</f>
-        <v>-1.1037277147487841</v>
-      </c>
-      <c r="Y7" s="16">
-        <f>[4]Model!$AS$42</f>
-        <v>0.12</v>
-      </c>
-      <c r="Z7" s="16">
-        <f>[4]Model!$AS$48</f>
-        <v>0.25873266742717416</v>
-      </c>
-      <c r="AA7" s="10" t="str">
-        <f>[4]Model!$AS$49</f>
-        <v>Slightly undervalued</v>
-      </c>
-      <c r="AB7" s="10"/>
-      <c r="AC7" s="10">
-        <v>1969</v>
-      </c>
-      <c r="AE7" s="17">
-        <f>[4]Main!$E$3</f>
-        <v>45751</v>
-      </c>
-      <c r="AF7" s="17">
-        <f>[4]Main!$G$3</f>
-        <v>45817</v>
-      </c>
-    </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>41</v>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>32</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="10">
-        <f>[5]Main!$D$3</f>
-        <v>1.21</v>
-      </c>
-      <c r="E9" s="13">
-        <f>[5]Main!$D$5</f>
-        <v>1119.492</v>
-      </c>
-      <c r="F9" s="13">
-        <f>[5]Main!$D$8</f>
-        <v>361</v>
-      </c>
-      <c r="G9" s="13">
-        <f>[5]Main!$D$9</f>
-        <v>758.49199999999996</v>
-      </c>
-      <c r="H9" s="13">
-        <f>[5]Model!Z$33</f>
-        <v>-1368.8</v>
-      </c>
-      <c r="I9" s="13">
-        <f>[5]Model!AA$33</f>
-        <v>-2104.9</v>
-      </c>
-      <c r="J9" s="13">
-        <f>[5]Model!AB$33</f>
-        <v>-722.21355000000028</v>
-      </c>
-      <c r="K9" s="13">
-        <f>[5]Model!AC$33</f>
-        <v>-504.726876</v>
-      </c>
-      <c r="L9" s="13">
-        <f>[5]Model!AD$33</f>
-        <v>-298.75576328999978</v>
-      </c>
-      <c r="M9" s="13">
-        <f>[5]Model!AE$33</f>
-        <v>-107.28387832140008</v>
-      </c>
-      <c r="N9" s="14">
-        <f t="shared" ref="N9" si="10">$G9/H9</f>
-        <v>-0.55412916423144354</v>
-      </c>
-      <c r="O9" s="14">
-        <f t="shared" ref="O9" si="11">$G9/I9</f>
-        <v>-0.36034585966079147</v>
-      </c>
-      <c r="P9" s="14">
-        <f t="shared" ref="P9" si="12">$G9/J9</f>
-        <v>-1.0502323031740399</v>
-      </c>
-      <c r="Q9" s="14">
-        <f t="shared" ref="Q9" si="13">$G9/K9</f>
-        <v>-1.5027771178168843</v>
-      </c>
-      <c r="R9" s="14">
-        <f t="shared" ref="R9" si="14">$G9/L9</f>
-        <v>-2.5388363780742798</v>
-      </c>
-      <c r="S9" s="14">
-        <f t="shared" ref="S9" si="15">$G9/M9</f>
-        <v>-7.0699532107491159</v>
-      </c>
-      <c r="T9" s="13">
-        <f>[5]Model!$Z$8</f>
-        <v>891.2</v>
-      </c>
-      <c r="U9" s="16">
-        <f>[5]Model!$Y$42</f>
-        <v>0.3960987261146498</v>
-      </c>
-      <c r="V9" s="16">
-        <f>[5]Model!$Z$42</f>
-        <v>0.27060165383518697</v>
-      </c>
-      <c r="W9" s="16">
-        <f>[5]Model!$Z$48</f>
-        <v>-0.56979353680430866</v>
-      </c>
-      <c r="X9" s="16">
-        <f>[5]Model!$Z$51</f>
-        <v>-1.5075179533213643</v>
-      </c>
-      <c r="Y9" s="16">
-        <f>[5]Model!$AP$39</f>
-        <v>0.1</v>
-      </c>
-      <c r="Z9" s="16">
-        <f>[5]Model!$AP$45</f>
-        <v>-0.26355921079086486</v>
-      </c>
-      <c r="AA9" s="10" t="str">
-        <f>[5]Model!$AP$46</f>
-        <v>Slightly overvalued</v>
-      </c>
-      <c r="AC9" s="10">
-        <v>1997</v>
-      </c>
-      <c r="AE9" s="18">
-        <f>[5]Main!$E$3</f>
-        <v>45751</v>
-      </c>
-      <c r="AF9" s="18">
-        <f>[5]Main!$G$3</f>
-        <v>45785</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{A639A081-823D-480C-B8E3-E8540E353F47}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{1E28E457-F855-40C5-9070-8BE0C79C6684}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{A73CB0F7-E51A-47D4-B42C-E9E12E13F561}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{A73CB0F7-E51A-47D4-B42C-E9E12E13F561}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{1C1D4293-4095-4A0E-A38F-07FACA5B80F2}"/>
-    <hyperlink ref="B9" r:id="rId5" xr:uid="{229D4175-EC51-46EF-B3C5-E9711257CB8D}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{229D4175-EC51-46EF-B3C5-E9711257CB8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
--- a/Financial Analysis/Models (Energy).xlsx
+++ b/Financial Analysis/Models (Energy).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E9C45D-455B-4F85-A42A-54425CA48A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AC4A36-80F8-48AC-9E53-536CFC5304E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{14D7A11B-4B63-41BA-92AC-B31B19EF0AA6}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Company</t>
   </si>
@@ -164,17 +164,21 @@
   </si>
   <si>
     <t>ISBS Var</t>
+  </si>
+  <si>
+    <t>2025 EV/R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="165" formatCode="0\x"/>
     <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -248,7 +252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -299,19 +303,16 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -562,96 +563,66 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>2.37</v>
+            <v>109.4</v>
           </cell>
           <cell r="E3">
             <v>45927</v>
           </cell>
           <cell r="G3">
-            <v>45972</v>
+            <v>45623</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2736.8760000000002</v>
+            <v>16147.44</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>506.29999999999973</v>
+            <v>683</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>2230.5760000000005</v>
+            <v>15464.44</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="8">
-          <cell r="AA8">
-            <v>628.79999999999995</v>
-          </cell>
-          <cell r="AB8">
-            <v>738.56</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="Z33">
-            <v>-1368.8</v>
-          </cell>
-          <cell r="AA33">
-            <v>-2104.9</v>
-          </cell>
-          <cell r="AB33">
-            <v>-910.35050000000001</v>
-          </cell>
-          <cell r="AC33">
-            <v>-508.71392100000014</v>
-          </cell>
-          <cell r="AD33">
-            <v>-351.38562542999983</v>
-          </cell>
-          <cell r="AE33">
-            <v>-191.72685569219993</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="AP39">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="AA42">
-            <v>-0.29443447037701986</v>
-          </cell>
-          <cell r="AB42">
-            <v>0.17455470737913492</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="AP45">
-            <v>-0.84446381726903419</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="AP46" t="str">
+        <row r="6">
+          <cell r="Q6"/>
+        </row>
+        <row r="17">
+          <cell r="Q17"/>
+          <cell r="R17">
+            <v>-73.699999999999989</v>
+          </cell>
+          <cell r="S17">
+            <v>-111.6</v>
+          </cell>
+          <cell r="T17">
+            <v>-131.6</v>
+          </cell>
+          <cell r="U17">
+            <v>-92.82</v>
+          </cell>
+          <cell r="V17">
+            <v>-33.285000000000011</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="AG23">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AG29">
+            <v>-0.83979249526057242</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AG30" t="str">
             <v>Heavily overvalued</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="AB48">
-            <v>-0.44518996425476615</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="AB51">
-            <v>-1.0778413399046796</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="P93">
-            <v>3353.8</v>
           </cell>
         </row>
       </sheetData>
@@ -674,62 +645,93 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>109.4</v>
+            <v>2.37</v>
           </cell>
           <cell r="E3">
             <v>45927</v>
           </cell>
           <cell r="G3">
-            <v>45623</v>
+            <v>45972</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>16147.44</v>
+            <v>2736.8760000000002</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>683</v>
+            <v>506.29999999999973</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>15464.44</v>
+            <v>2230.5760000000005</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="17">
-          <cell r="R17">
-            <v>-73.699999999999989</v>
-          </cell>
-          <cell r="S17">
-            <v>-111.6</v>
-          </cell>
-          <cell r="T17">
-            <v>-131.6</v>
-          </cell>
-          <cell r="U17">
-            <v>-92.82</v>
-          </cell>
-          <cell r="V17">
-            <v>-33.285000000000011</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="AG23">
-            <v>0.09</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="AG29">
-            <v>-0.83979249526057242</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AG30" t="str">
+        <row r="8">
+          <cell r="AB8">
+            <v>738.56</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Z33">
+            <v>-1368.8</v>
+          </cell>
+          <cell r="AA33">
+            <v>-2104.9</v>
+          </cell>
+          <cell r="AB33">
+            <v>-910.35050000000001</v>
+          </cell>
+          <cell r="AC33">
+            <v>-508.71392100000014</v>
+          </cell>
+          <cell r="AD33">
+            <v>-351.38562542999983</v>
+          </cell>
+          <cell r="AE33">
+            <v>-191.72685569219993</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="AP39">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="AA42">
+            <v>-0.29443447037701986</v>
+          </cell>
+          <cell r="AB42">
+            <v>0.17455470737913492</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AP45">
+            <v>-0.84446381726903419</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="AP46" t="str">
             <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="AB48">
+            <v>-0.44518996425476615</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="AB51">
+            <v>-1.0778413399046796</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="P93">
+            <v>3353.8</v>
           </cell>
         </row>
       </sheetData>
@@ -816,18 +818,10 @@
             <v>0.4270944741532976</v>
           </cell>
         </row>
-        <row r="49">
-          <cell r="AS49">
-            <v>-0.99110072258398429</v>
-          </cell>
-        </row>
         <row r="50">
           <cell r="AE50">
             <v>-0.15485885585810655</v>
           </cell>
-          <cell r="AS50" t="str">
-            <v>Overvalued</v>
-          </cell>
         </row>
         <row r="53">
           <cell r="AE53">
@@ -837,6 +831,16 @@
         <row r="85">
           <cell r="AE85">
             <v>830.6</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="AS129">
+            <v>-4.329644050409831E-2</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="AS130" t="str">
+            <v>Fairly valued</v>
           </cell>
         </row>
       </sheetData>
@@ -1142,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F50123-7912-4358-B5CC-BC69536C3F1F}">
-  <dimension ref="B2:AG9"/>
+  <dimension ref="B2:AH9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
@@ -1156,16 +1160,17 @@
     <col min="14" max="18" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="9.5546875" customWidth="1"/>
     <col min="22" max="22" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.109375" customWidth="1"/>
-    <col min="30" max="30" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.109375" customWidth="1"/>
+    <col min="31" max="31" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1229,39 +1234,42 @@
       <c r="V2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
@@ -1296,44 +1304,45 @@
         <f t="shared" si="0"/>
         <v>0.73931484502446998</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="22">
         <f>TRIMMEAN(S4:S1048576,80%)</f>
         <v>1.3705397872823148</v>
       </c>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
       <c r="V3" s="7"/>
-      <c r="W3" s="8">
-        <f>TRIMMEAN(W4:W1048576,80%)</f>
+      <c r="W3" s="7"/>
+      <c r="X3" s="8">
+        <f t="shared" ref="X3:AC3" si="1">TRIMMEAN(X4:X1048576,80%)</f>
         <v>-5.4177702865398469E-2</v>
       </c>
-      <c r="X3" s="8">
-        <f>TRIMMEAN(X4:X1048576,80%)</f>
+      <c r="Y3" s="8">
+        <f t="shared" si="1"/>
         <v>0.17455470737913492</v>
       </c>
-      <c r="Y3" s="8">
-        <f>TRIMMEAN(Y4:Y1048576,80%)</f>
+      <c r="Z3" s="8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z3" s="8">
-        <f>TRIMMEAN(Z4:Z1048576,80%)</f>
+      <c r="AA3" s="8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA3" s="8">
-        <f>TRIMMEAN(AA4:AA1048576,80%)</f>
+      <c r="AB3" s="8">
+        <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
-      <c r="AB3" s="8">
-        <f>TRIMMEAN(AB4:AB1048576,80%)</f>
-        <v>-0.83979249526057242</v>
-      </c>
-      <c r="AC3" s="9" t="str">
-        <f>INDEX(AC4:AC8,MODE(MATCH(AC4:AC8,AC4:AC8,0)))</f>
+      <c r="AC3" s="8">
+        <f t="shared" si="1"/>
+        <v>-0.83830827653230344</v>
+      </c>
+      <c r="AD3" s="9" t="str">
+        <f>INDEX(AD4:AD8,MODE(MATCH(AD4:AD8,AD4:AD8,0)))</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
     </row>
-    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>24</v>
       </c>
@@ -1385,22 +1394,22 @@
         <v>29.424473543559593</v>
       </c>
       <c r="O4" s="14">
-        <f t="shared" ref="O4" si="1">$G4/J4</f>
+        <f t="shared" ref="O4" si="2">$G4/J4</f>
         <v>49.972584386681802</v>
       </c>
       <c r="P4" s="14">
-        <f t="shared" ref="P4" si="2">$G4/K4</f>
+        <f t="shared" ref="P4" si="3">$G4/K4</f>
         <v>28.297408332907111</v>
       </c>
       <c r="Q4" s="14">
-        <f t="shared" ref="Q4" si="3">$G4/L4</f>
+        <f t="shared" ref="Q4" si="4">$G4/L4</f>
         <v>26.017564788353763</v>
       </c>
       <c r="R4" s="14">
-        <f t="shared" ref="R4" si="4">$G4/M4</f>
+        <f t="shared" ref="R4" si="5">$G4/M4</f>
         <v>24.428282956464795</v>
       </c>
-      <c r="S4" s="23">
+      <c r="S4" s="21">
         <f>G4/[1]Model!$L$42</f>
         <v>2.0759904219616123</v>
       </c>
@@ -1409,54 +1418,58 @@
         <v>-0.51830220919078429</v>
       </c>
       <c r="U4" s="15">
-        <f>AVERAGE(T4,AB4)</f>
+        <f>AVERAGE(T4,AC4)</f>
         <v>-0.46241934260731044</v>
       </c>
       <c r="V4" s="13">
         <f>[1]Model!$U$3</f>
         <v>25809.200000000001</v>
       </c>
-      <c r="W4" s="15">
+      <c r="W4" s="23">
+        <f>G4/V4</f>
+        <v>4.2661678781209798</v>
+      </c>
+      <c r="X4" s="15">
         <f>[1]Model!T$19</f>
         <v>-5.4177702865398469E-2</v>
       </c>
-      <c r="X4" s="15">
+      <c r="Y4" s="15">
         <f>[1]Model!U$19</f>
         <v>9.5095044127630812E-2</v>
       </c>
-      <c r="Y4" s="15">
+      <c r="Z4" s="15">
         <f>[1]Model!$U$22</f>
         <v>0.18578801357655411</v>
       </c>
-      <c r="Z4" s="15">
+      <c r="AA4" s="15">
         <f>[1]Model!$U$23</f>
         <v>0.12163589727694003</v>
       </c>
-      <c r="AA4" s="15">
+      <c r="AB4" s="15">
         <f>[1]Model!$AH$21</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AB4" s="15">
+      <c r="AC4" s="15">
         <f>[1]Model!$AH$27</f>
         <v>-0.40653647602383658</v>
       </c>
-      <c r="AC4" s="10" t="str">
+      <c r="AD4" s="10" t="str">
         <f>[1]Model!$AH$28</f>
         <v>Overvalued</v>
       </c>
-      <c r="AD4" s="10">
+      <c r="AE4" s="10">
         <v>1999</v>
       </c>
-      <c r="AF4" s="17">
+      <c r="AG4" s="17">
         <f>[1]Main!$E$3</f>
         <v>45909</v>
       </c>
-      <c r="AG4" s="17">
+      <c r="AH4" s="17">
         <f>[1]Main!$G$3</f>
         <v>45971</v>
       </c>
     </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>25</v>
       </c>
@@ -1508,22 +1521,22 @@
         <v>-581.11879194630376</v>
       </c>
       <c r="O5" s="14">
-        <f>$G5/J5</f>
+        <f t="shared" ref="O5:R7" si="6">$G5/J5</f>
         <v>401.05624612516942</v>
       </c>
       <c r="P5" s="14">
-        <f>$G5/K5</f>
+        <f t="shared" si="6"/>
         <v>119.26999314050528</v>
       </c>
       <c r="Q5" s="14">
-        <f>$G5/L5</f>
+        <f t="shared" si="6"/>
         <v>91.800395935171267</v>
       </c>
       <c r="R5" s="14">
-        <f>$G5/M5</f>
+        <f t="shared" si="6"/>
         <v>73.18093393282949</v>
       </c>
-      <c r="S5" s="23">
+      <c r="S5" s="21">
         <f>G5/[2]Model!$P$83</f>
         <v>6.8434459592965817</v>
       </c>
@@ -1532,54 +1545,58 @@
         <v>-0.8538747867744122</v>
       </c>
       <c r="U5" s="15">
-        <f>AVERAGE(T5,AB5)</f>
+        <f>AVERAGE(T5,AC5)</f>
         <v>-0.84609153165335782</v>
       </c>
-      <c r="V5" s="20">
+      <c r="V5" s="13">
         <f>[2]Model!$Y$7</f>
         <v>1751.5670000000002</v>
       </c>
-      <c r="W5" s="21">
+      <c r="W5" s="23">
+        <f t="shared" ref="W5:W8" si="7">G5/V5</f>
+        <v>9.8867699608407769</v>
+      </c>
+      <c r="X5" s="15">
         <f>[2]Model!X$36</f>
         <v>0.10537763444086101</v>
       </c>
-      <c r="X5" s="21">
+      <c r="Y5" s="15">
         <f>[2]Model!Y$36</f>
         <v>0.18846994164744224</v>
       </c>
-      <c r="Y5" s="21">
+      <c r="Z5" s="15">
         <f>[2]Model!$Y$41</f>
         <v>0.3176466158588282</v>
       </c>
-      <c r="Z5" s="21">
+      <c r="AA5" s="15">
         <f>[2]Model!$Y$45</f>
         <v>5.5310090907170664E-2</v>
       </c>
-      <c r="AA5" s="15">
+      <c r="AB5" s="15">
         <f>[2]Model!$AM$34</f>
         <v>0.09</v>
       </c>
-      <c r="AB5" s="15">
+      <c r="AC5" s="15">
         <f>[2]Model!$AM$40</f>
         <v>-0.83830827653230344</v>
       </c>
-      <c r="AC5" s="10" t="str">
+      <c r="AD5" s="10" t="str">
         <f>[2]Model!$AM$41</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AD5" s="10">
+      <c r="AE5" s="10">
         <v>2001</v>
       </c>
-      <c r="AF5" s="17">
+      <c r="AG5" s="17">
         <f>[2]Main!$E$3</f>
         <v>45927</v>
       </c>
-      <c r="AG5" s="17">
+      <c r="AH5" s="17">
         <f>[2]Main!$G$3</f>
         <v>45960</v>
       </c>
     </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>22</v>
       </c>
@@ -1587,43 +1604,43 @@
         <v>29</v>
       </c>
       <c r="D6" s="12">
-        <f>[4]Main!$D$3</f>
+        <f>[3]Main!$D$3</f>
         <v>109.4</v>
       </c>
       <c r="E6" s="13">
-        <f>[4]Main!$D$5</f>
+        <f>[3]Main!$D$5</f>
         <v>16147.44</v>
       </c>
       <c r="F6" s="13">
-        <f>[4]Main!$D$8</f>
+        <f>[3]Main!$D$8</f>
         <v>683</v>
       </c>
       <c r="G6" s="13">
-        <f>[4]Main!$D$9</f>
+        <f>[3]Main!$D$9</f>
         <v>15464.44</v>
       </c>
       <c r="H6" s="13">
-        <f>[4]Model!Q$17</f>
+        <f>[3]Model!Q$17</f>
         <v>0</v>
       </c>
       <c r="I6" s="13">
-        <f>[4]Model!R$17</f>
+        <f>[3]Model!R$17</f>
         <v>-73.699999999999989</v>
       </c>
       <c r="J6" s="13">
-        <f>[4]Model!S$17</f>
+        <f>[3]Model!S$17</f>
         <v>-111.6</v>
       </c>
       <c r="K6" s="13">
-        <f>[4]Model!T$17</f>
+        <f>[3]Model!T$17</f>
         <v>-131.6</v>
       </c>
       <c r="L6" s="13">
-        <f>[4]Model!U$17</f>
+        <f>[3]Model!U$17</f>
         <v>-92.82</v>
       </c>
       <c r="M6" s="13">
-        <f>[4]Model!V$17</f>
+        <f>[3]Model!V$17</f>
         <v>-33.285000000000011</v>
       </c>
       <c r="N6" s="14">
@@ -1631,69 +1648,70 @@
         <v>-209.82957937584808</v>
       </c>
       <c r="O6" s="14">
-        <f>$G6/J6</f>
+        <f t="shared" si="6"/>
         <v>-138.57025089605736</v>
       </c>
       <c r="P6" s="14">
-        <f>$G6/K6</f>
+        <f t="shared" si="6"/>
         <v>-117.51094224924013</v>
       </c>
       <c r="Q6" s="14">
-        <f>$G6/L6</f>
+        <f t="shared" si="6"/>
         <v>-166.6067657832364</v>
       </c>
       <c r="R6" s="14">
-        <f>$G6/M6</f>
+        <f t="shared" si="6"/>
         <v>-464.606879975965</v>
       </c>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
       <c r="V6" s="18">
-        <f>[4]Model!$Q$6</f>
+        <f>[3]Model!$Q$6</f>
         <v>0</v>
       </c>
-      <c r="W6" s="19">
-        <f>[4]Model!$P$22</f>
+      <c r="W6" s="23"/>
+      <c r="X6" s="19">
+        <f>[3]Model!$P$22</f>
         <v>0</v>
       </c>
-      <c r="X6" s="19">
-        <f>[4]Model!$Q$22</f>
+      <c r="Y6" s="19">
+        <f>[3]Model!$Q$22</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="19">
-        <f>[4]Model!$Q$23</f>
+      <c r="Z6" s="19">
+        <f>[3]Model!$Q$23</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="19">
-        <f>[4]Model!$Q$26</f>
+      <c r="AA6" s="19">
+        <f>[3]Model!$Q$26</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="15">
-        <f>[4]Model!$AG$23</f>
+      <c r="AB6" s="15">
+        <f>[3]Model!$AG$23</f>
         <v>0.09</v>
       </c>
-      <c r="AB6" s="15">
-        <f>[4]Model!$AG$29</f>
+      <c r="AC6" s="15">
+        <f>[3]Model!$AG$29</f>
         <v>-0.83979249526057242</v>
       </c>
-      <c r="AC6" s="15" t="str">
-        <f>[4]Model!$AG$30</f>
+      <c r="AD6" s="15" t="str">
+        <f>[3]Model!$AG$30</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AD6" s="10">
+      <c r="AE6" s="10">
         <v>2013</v>
       </c>
-      <c r="AF6" s="16">
-        <f>[4]Main!$E$3</f>
+      <c r="AG6" s="16">
+        <f>[3]Main!$E$3</f>
         <v>45927</v>
       </c>
-      <c r="AG6" s="16">
-        <f>[4]Main!$G$3</f>
+      <c r="AH6" s="16">
+        <f>[3]Main!$G$3</f>
         <v>45623</v>
       </c>
     </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>34</v>
       </c>
@@ -1701,43 +1719,43 @@
         <v>35</v>
       </c>
       <c r="D7" s="12">
-        <f>[3]Main!$D$3</f>
+        <f>[4]Main!$D$3</f>
         <v>2.37</v>
       </c>
       <c r="E7" s="13">
-        <f>[3]Main!$D$5</f>
+        <f>[4]Main!$D$5</f>
         <v>2736.8760000000002</v>
       </c>
       <c r="F7" s="13">
-        <f>[3]Main!$D$8</f>
+        <f>[4]Main!$D$8</f>
         <v>506.29999999999973</v>
       </c>
       <c r="G7" s="13">
-        <f>[3]Main!$D$9</f>
+        <f>[4]Main!$D$9</f>
         <v>2230.5760000000005</v>
       </c>
       <c r="H7" s="13">
-        <f>[3]Model!Z$33</f>
+        <f>[4]Model!Z$33</f>
         <v>-1368.8</v>
       </c>
       <c r="I7" s="13">
-        <f>[3]Model!AA$33</f>
+        <f>[4]Model!AA$33</f>
         <v>-2104.9</v>
       </c>
       <c r="J7" s="13">
-        <f>[3]Model!AB$33</f>
+        <f>[4]Model!AB$33</f>
         <v>-910.35050000000001</v>
       </c>
       <c r="K7" s="13">
-        <f>[3]Model!AC$33</f>
+        <f>[4]Model!AC$33</f>
         <v>-508.71392100000014</v>
       </c>
       <c r="L7" s="13">
-        <f>[3]Model!AD$33</f>
+        <f>[4]Model!AD$33</f>
         <v>-351.38562542999983</v>
       </c>
       <c r="M7" s="13">
-        <f>[3]Model!AE$33</f>
+        <f>[4]Model!AE$33</f>
         <v>-191.72685569219993</v>
       </c>
       <c r="N7" s="14">
@@ -1745,78 +1763,82 @@
         <v>-1.0597063993538887</v>
       </c>
       <c r="O7" s="14">
-        <f>$G7/J7</f>
+        <f t="shared" si="6"/>
         <v>-2.4502386718082767</v>
       </c>
       <c r="P7" s="14">
-        <f>$G7/K7</f>
+        <f t="shared" si="6"/>
         <v>-4.3847355221088984</v>
       </c>
       <c r="Q7" s="14">
-        <f>$G7/L7</f>
+        <f t="shared" si="6"/>
         <v>-6.3479432241156308</v>
       </c>
       <c r="R7" s="14">
-        <f>$G7/M7</f>
+        <f t="shared" si="6"/>
         <v>-11.634134362381594</v>
       </c>
-      <c r="S7" s="23">
-        <f>G7/[3]Model!$P$93</f>
+      <c r="S7" s="21">
+        <f>G7/[4]Model!$P$93</f>
         <v>0.6650891526030176</v>
       </c>
       <c r="T7" s="15">
-        <f>[3]Model!$P$93/G7-1</f>
+        <f>[4]Model!$P$93/G7-1</f>
         <v>0.50355782542267091</v>
       </c>
       <c r="U7" s="15">
-        <f t="shared" ref="U7:U8" si="5">AVERAGE(T7,AB7)</f>
+        <f>AVERAGE(T7,AC7)</f>
         <v>-0.17045299592318164</v>
       </c>
-      <c r="V7" s="20">
-        <f>[3]Model!$AB$8</f>
+      <c r="V7" s="13">
+        <f>[4]Model!$AB$8</f>
         <v>738.56</v>
       </c>
-      <c r="W7" s="21">
-        <f>[3]Model!AA$42</f>
+      <c r="W7" s="23">
+        <f t="shared" si="7"/>
+        <v>3.0201689774696714</v>
+      </c>
+      <c r="X7" s="15">
+        <f>[4]Model!AA$42</f>
         <v>-0.29443447037701986</v>
       </c>
-      <c r="X7" s="21">
-        <f>[3]Model!AB$42</f>
+      <c r="Y7" s="15">
+        <f>[4]Model!AB$42</f>
         <v>0.17455470737913492</v>
       </c>
-      <c r="Y7" s="21">
-        <f>[3]Model!$AB$48</f>
+      <c r="Z7" s="15">
+        <f>[4]Model!$AB$48</f>
         <v>-0.44518996425476615</v>
       </c>
-      <c r="Z7" s="21">
-        <f>[3]Model!$AB$51</f>
+      <c r="AA7" s="15">
+        <f>[4]Model!$AB$51</f>
         <v>-1.0778413399046796</v>
       </c>
-      <c r="AA7" s="15">
-        <f>[3]Model!$AP$39</f>
+      <c r="AB7" s="15">
+        <f>[4]Model!$AP$39</f>
         <v>0.1</v>
       </c>
-      <c r="AB7" s="15">
-        <f>[3]Model!$AP$45</f>
+      <c r="AC7" s="15">
+        <f>[4]Model!$AP$45</f>
         <v>-0.84446381726903419</v>
       </c>
-      <c r="AC7" s="10" t="str">
-        <f>[3]Model!$AP$46</f>
+      <c r="AD7" s="10" t="str">
+        <f>[4]Model!$AP$46</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AD7" s="10">
+      <c r="AE7" s="10">
         <v>1997</v>
       </c>
-      <c r="AF7" s="17">
-        <f>[3]Main!$E$3</f>
+      <c r="AG7" s="17">
+        <f>[4]Main!$E$3</f>
         <v>45927</v>
       </c>
-      <c r="AG7" s="17">
-        <f>[3]Main!$G$3</f>
+      <c r="AH7" s="17">
+        <f>[4]Main!$G$3</f>
         <v>45972</v>
       </c>
     </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>23</v>
       </c>
@@ -1864,26 +1886,26 @@
         <v>122.6</v>
       </c>
       <c r="N8" s="14">
-        <f t="shared" ref="N8" si="6">$G8/I8</f>
+        <f t="shared" ref="N8" si="8">$G8/I8</f>
         <v>2.8866242038216563</v>
       </c>
       <c r="O8" s="14">
-        <f t="shared" ref="O8" si="7">$G8/J8</f>
+        <f t="shared" ref="O8" si="9">$G8/J8</f>
         <v>1.838539553752536</v>
       </c>
       <c r="P8" s="14">
-        <f t="shared" ref="P8" si="8">$G8/K8</f>
+        <f t="shared" ref="P8" si="10">$G8/K8</f>
         <v>0.79300087489063886</v>
       </c>
       <c r="Q8" s="14">
-        <f t="shared" ref="Q8" si="9">$G8/L8</f>
+        <f t="shared" ref="Q8" si="11">$G8/L8</f>
         <v>0.72165605095541419</v>
       </c>
       <c r="R8" s="14">
-        <f t="shared" ref="R8" si="10">$G8/M8</f>
+        <f t="shared" ref="R8" si="12">$G8/M8</f>
         <v>0.73931484502446998</v>
       </c>
-      <c r="S8" s="23">
+      <c r="S8" s="21">
         <f>G8/[5]Model!$AE$85</f>
         <v>0.10912593306043825</v>
       </c>
@@ -1892,54 +1914,58 @@
         <v>8.1637246248896727</v>
       </c>
       <c r="U8" s="15">
-        <f t="shared" si="5"/>
-        <v>3.5863119511528443</v>
-      </c>
-      <c r="V8" s="22">
+        <f>AVERAGE(T8,AC8)</f>
+        <v>4.0602140921927869</v>
+      </c>
+      <c r="V8" s="20">
         <f>[5]Model!$AE$13</f>
         <v>160.12</v>
       </c>
-      <c r="W8" s="21">
+      <c r="W8" s="23">
+        <f t="shared" si="7"/>
+        <v>0.56607544341743699</v>
+      </c>
+      <c r="X8" s="15">
         <f>[5]Model!$AD$45</f>
         <v>-9.0761750405186525E-2</v>
       </c>
-      <c r="X8" s="21">
+      <c r="Y8" s="15">
         <f>[5]Model!$AE$45</f>
         <v>0.4270944741532976</v>
       </c>
-      <c r="Y8" s="21">
+      <c r="Z8" s="15">
         <f>[5]Model!$AE$50</f>
         <v>-0.15485885585810655</v>
       </c>
-      <c r="Z8" s="21">
+      <c r="AA8" s="15">
         <f>[5]Model!$AE$53</f>
         <v>-1.2246814888833375</v>
       </c>
-      <c r="AA8" s="15">
+      <c r="AB8" s="15">
         <f>[5]Model!$AS$43</f>
         <v>0.12</v>
       </c>
-      <c r="AB8" s="15">
-        <f>[5]Model!$AS$49</f>
-        <v>-0.99110072258398429</v>
-      </c>
-      <c r="AC8" s="10" t="str">
-        <f>[5]Model!$AS$50</f>
-        <v>Overvalued</v>
-      </c>
-      <c r="AD8" s="10">
+      <c r="AC8" s="15">
+        <f>[5]Model!$AS$129</f>
+        <v>-4.329644050409831E-2</v>
+      </c>
+      <c r="AD8" s="10" t="str">
+        <f>[5]Model!$AS$130</f>
+        <v>Fairly valued</v>
+      </c>
+      <c r="AE8" s="10">
         <v>1969</v>
       </c>
-      <c r="AF8" s="16">
+      <c r="AG8" s="16">
         <f>[5]Main!$E$3</f>
         <v>45927</v>
       </c>
-      <c r="AG8" s="16">
+      <c r="AH8" s="16">
         <f>[5]Main!$G$3</f>
         <v>45912</v>
       </c>
     </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>32</v>
       </c>

--- a/Financial Analysis/Models (Energy).xlsx
+++ b/Financial Analysis/Models (Energy).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AC4A36-80F8-48AC-9E53-536CFC5304E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB03C915-4606-4333-A5F3-2D4AE3C005EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{14D7A11B-4B63-41BA-92AC-B31B19EF0AA6}"/>
   </bookViews>
@@ -252,7 +252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -315,6 +315,9 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -569,7 +572,7 @@
             <v>45927</v>
           </cell>
           <cell r="G3">
-            <v>45623</v>
+            <v>45988</v>
           </cell>
         </row>
         <row r="5">
@@ -589,11 +592,7 @@
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="6">
-          <cell r="Q6"/>
-        </row>
         <row r="17">
-          <cell r="Q17"/>
           <cell r="R17">
             <v>-73.699999999999989</v>
           </cell>
@@ -623,6 +622,16 @@
         <row r="30">
           <cell r="AG30" t="str">
             <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="L55">
+            <v>21.155184678522573</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="L56">
+            <v>-0.95273026375348868</v>
           </cell>
         </row>
       </sheetData>
@@ -672,6 +681,9 @@
       </sheetData>
       <sheetData sheetId="1">
         <row r="8">
+          <cell r="AA8">
+            <v>628.79999999999995</v>
+          </cell>
           <cell r="AB8">
             <v>738.56</v>
           </cell>
@@ -1306,10 +1318,16 @@
       </c>
       <c r="S3" s="22">
         <f>TRIMMEAN(S4:S1048576,80%)</f>
-        <v>1.3705397872823148</v>
-      </c>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
+        <v>2.0759904219616123</v>
+      </c>
+      <c r="T3" s="8">
+        <f>TRIMMEAN(T4:T1048576,80%)</f>
+        <v>-0.51830220919078429</v>
+      </c>
+      <c r="U3" s="8">
+        <f>TRIMMEAN(U4:U1048576,80%)</f>
+        <v>-0.46241934260731044</v>
+      </c>
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="8">
@@ -1663,9 +1681,18 @@
         <f t="shared" si="6"/>
         <v>-464.606879975965</v>
       </c>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
+      <c r="S6" s="21">
+        <f>[3]Model!$L$55</f>
+        <v>21.155184678522573</v>
+      </c>
+      <c r="T6" s="24">
+        <f>[3]Model!$L$56</f>
+        <v>-0.95273026375348868</v>
+      </c>
+      <c r="U6" s="15">
+        <f>AVERAGE(T6,AC6)</f>
+        <v>-0.89626137950703055</v>
+      </c>
       <c r="V6" s="18">
         <f>[3]Model!$Q$6</f>
         <v>0</v>
@@ -1708,7 +1735,7 @@
       </c>
       <c r="AH6" s="16">
         <f>[3]Main!$G$3</f>
-        <v>45623</v>
+        <v>45988</v>
       </c>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.3">

--- a/Financial Analysis/Models (Energy).xlsx
+++ b/Financial Analysis/Models (Energy).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB03C915-4606-4333-A5F3-2D4AE3C005EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B352EE1-D63D-44E7-A34A-0B905A3D8257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{14D7A11B-4B63-41BA-92AC-B31B19EF0AA6}"/>
   </bookViews>
@@ -252,7 +252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -315,9 +315,6 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -350,10 +347,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>332.45</v>
+            <v>384.26</v>
           </cell>
           <cell r="E3">
-            <v>45909</v>
+            <v>45950</v>
           </cell>
           <cell r="G3">
             <v>45971</v>
@@ -361,7 +358,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>103857.37999999999</v>
+            <v>120042.82399999999</v>
           </cell>
         </row>
         <row r="8">
@@ -371,7 +368,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>110106.37999999999</v>
+            <v>126291.82399999999</v>
           </cell>
         </row>
       </sheetData>
@@ -426,7 +423,7 @@
         </row>
         <row r="27">
           <cell r="AH27">
-            <v>-0.40653647602383658</v>
+            <v>-0.48655350922324592</v>
           </cell>
         </row>
         <row r="28">
@@ -459,35 +456,35 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>70.709999999999994</v>
+            <v>132.12</v>
           </cell>
           <cell r="E3">
-            <v>45927</v>
+            <v>45959</v>
           </cell>
           <cell r="G3">
-            <v>45960</v>
+            <v>46058</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>16546.14</v>
+            <v>31246.38</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-771.2</v>
+            <v>-745.59999999999991</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>17317.34</v>
+            <v>31991.98</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="7">
           <cell r="Y7">
-            <v>1751.5670000000002</v>
+            <v>1976.9399999999998</v>
           </cell>
         </row>
         <row r="28">
@@ -498,16 +495,16 @@
             <v>-29.800000000000253</v>
           </cell>
           <cell r="Y28">
-            <v>43.17933000000022</v>
+            <v>9.224400000000152</v>
           </cell>
           <cell r="Z28">
-            <v>145.19444115000002</v>
+            <v>215.01444689999951</v>
           </cell>
           <cell r="AA28">
-            <v>188.6412343169998</v>
+            <v>301.22465602799997</v>
           </cell>
           <cell r="AB28">
-            <v>236.63731889367591</v>
+            <v>380.12981731463947</v>
           </cell>
         </row>
         <row r="34">
@@ -520,17 +517,17 @@
             <v>0.10537763444086101</v>
           </cell>
           <cell r="Y36">
-            <v>0.18846994164744224</v>
+            <v>0.34138960510245608</v>
           </cell>
         </row>
         <row r="40">
           <cell r="AM40">
-            <v>-0.83830827653230344</v>
+            <v>-0.7852827016272812</v>
           </cell>
         </row>
         <row r="41">
           <cell r="Y41">
-            <v>0.3176466158588282</v>
+            <v>0.31610691270347108</v>
           </cell>
           <cell r="AM41" t="str">
             <v>Heavily overvalued</v>
@@ -538,12 +535,12 @@
         </row>
         <row r="45">
           <cell r="Y45">
-            <v>5.5310090907170664E-2</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="P83">
-            <v>2530.5</v>
+            <v>4.4829079284146284E-2</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="Q65">
+            <v>2638.2</v>
           </cell>
         </row>
       </sheetData>
@@ -566,10 +563,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>109.4</v>
+            <v>139.09</v>
           </cell>
           <cell r="E3">
-            <v>45927</v>
+            <v>45939</v>
           </cell>
           <cell r="G3">
             <v>45988</v>
@@ -577,7 +574,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>16147.44</v>
+            <v>20529.684000000001</v>
           </cell>
         </row>
         <row r="8">
@@ -587,12 +584,16 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>15464.44</v>
+            <v>19846.684000000001</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="6">
+          <cell r="Q6"/>
+        </row>
         <row r="17">
+          <cell r="Q17"/>
           <cell r="R17">
             <v>-73.699999999999989</v>
           </cell>
@@ -616,7 +617,7 @@
         </row>
         <row r="29">
           <cell r="AG29">
-            <v>-0.83979249526057242</v>
+            <v>-0.87399021483576544</v>
           </cell>
         </row>
         <row r="30">
@@ -626,12 +627,12 @@
         </row>
         <row r="55">
           <cell r="L55">
-            <v>21.155184678522573</v>
+            <v>27.150046511627909</v>
           </cell>
         </row>
         <row r="56">
           <cell r="L56">
-            <v>-0.95273026375348868</v>
+            <v>-0.9631676505757838</v>
           </cell>
         </row>
       </sheetData>
@@ -654,10 +655,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>2.37</v>
+            <v>3.51</v>
           </cell>
           <cell r="E3">
-            <v>45927</v>
+            <v>45950</v>
           </cell>
           <cell r="G3">
             <v>45972</v>
@@ -665,7 +666,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2736.8760000000002</v>
+            <v>4053.3479999999995</v>
           </cell>
         </row>
         <row r="8">
@@ -675,15 +676,12 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>2230.5760000000005</v>
+            <v>3547.0479999999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="8">
-          <cell r="AA8">
-            <v>628.79999999999995</v>
-          </cell>
           <cell r="AB8">
             <v>738.56</v>
           </cell>
@@ -723,7 +721,7 @@
         </row>
         <row r="45">
           <cell r="AP45">
-            <v>-0.84446381726903419</v>
+            <v>-0.89497984242951878</v>
           </cell>
         </row>
         <row r="46">
@@ -766,18 +764,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>7.85</v>
+            <v>7.81</v>
           </cell>
           <cell r="E3">
-            <v>45927</v>
+            <v>45959</v>
           </cell>
           <cell r="G3">
-            <v>45912</v>
+            <v>46009</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>191.54</v>
+            <v>190.56399999999999</v>
           </cell>
         </row>
         <row r="8">
@@ -787,7 +785,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>90.640000000000015</v>
+            <v>89.664000000000016</v>
           </cell>
         </row>
       </sheetData>
@@ -847,7 +845,7 @@
         </row>
         <row r="129">
           <cell r="AS129">
-            <v>-4.329644050409831E-2</v>
+            <v>-3.8396550314618638E-2</v>
           </cell>
         </row>
         <row r="130">
@@ -1298,35 +1296,35 @@
       <c r="M3" s="2"/>
       <c r="N3" s="6">
         <f>TRIMMEAN(N4:N1048576,80%)</f>
-        <v>-1.0597063993538887</v>
+        <v>-1.6851384863889018</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" ref="O3:R3" si="0">TRIMMEAN(O4:O1048576,80%)</f>
-        <v>1.838539553752536</v>
+        <v>1.8187423935091283</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>0.79300087489063886</v>
+        <v>0.78446194225721799</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>0.72165605095541419</v>
+        <v>0.71388535031847145</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>0.73931484502446998</v>
+        <v>0.73135399673735746</v>
       </c>
       <c r="S3" s="22">
         <f>TRIMMEAN(S4:S1048576,80%)</f>
-        <v>2.0759904219616123</v>
+        <v>2.381157358874769</v>
       </c>
       <c r="T3" s="8">
         <f>TRIMMEAN(T4:T1048576,80%)</f>
-        <v>-0.51830220919078429</v>
+        <v>-0.58003615499289962</v>
       </c>
       <c r="U3" s="8">
         <f>TRIMMEAN(U4:U1048576,80%)</f>
-        <v>-0.46241934260731044</v>
+        <v>-0.53329483210807282</v>
       </c>
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
@@ -1352,7 +1350,7 @@
       </c>
       <c r="AC3" s="8">
         <f t="shared" si="1"/>
-        <v>-0.83830827653230344</v>
+        <v>-0.7852827016272812</v>
       </c>
       <c r="AD3" s="9" t="str">
         <f>INDEX(AD4:AD8,MODE(MATCH(AD4:AD8,AD4:AD8,0)))</f>
@@ -1369,11 +1367,11 @@
       </c>
       <c r="D4" s="12">
         <f>[1]Main!$D$3</f>
-        <v>332.45</v>
+        <v>384.26</v>
       </c>
       <c r="E4" s="13">
         <f>[1]Main!$D$5</f>
-        <v>103857.37999999999</v>
+        <v>120042.82399999999</v>
       </c>
       <c r="F4" s="13">
         <f>[1]Main!$D$8</f>
@@ -1381,7 +1379,7 @@
       </c>
       <c r="G4" s="13">
         <f>[1]Main!$D$9</f>
-        <v>110106.37999999999</v>
+        <v>126291.82399999999</v>
       </c>
       <c r="H4" s="13">
         <f>[1]Model!S$15</f>
@@ -1409,35 +1407,35 @@
       </c>
       <c r="N4" s="14">
         <f>$G4/I4</f>
-        <v>29.424473543559593</v>
+        <v>33.749819347942278</v>
       </c>
       <c r="O4" s="14">
         <f t="shared" ref="O4" si="2">$G4/J4</f>
-        <v>49.972584386681802</v>
+        <v>57.318466306747766</v>
       </c>
       <c r="P4" s="14">
         <f t="shared" ref="P4" si="3">$G4/K4</f>
-        <v>28.297408332907111</v>
+        <v>32.457077535703547</v>
       </c>
       <c r="Q4" s="14">
         <f t="shared" ref="Q4" si="4">$G4/L4</f>
-        <v>26.017564788353763</v>
+        <v>29.842101004132282</v>
       </c>
       <c r="R4" s="14">
         <f t="shared" ref="R4" si="5">$G4/M4</f>
-        <v>24.428282956464795</v>
+        <v>28.019197541142045</v>
       </c>
       <c r="S4" s="21">
         <f>G4/[1]Model!$L$42</f>
-        <v>2.0759904219616123</v>
+        <v>2.381157358874769</v>
       </c>
       <c r="T4" s="15">
         <f>[1]Model!$L$42/G4-1</f>
-        <v>-0.51830220919078429</v>
+        <v>-0.58003615499289962</v>
       </c>
       <c r="U4" s="15">
         <f>AVERAGE(T4,AC4)</f>
-        <v>-0.46241934260731044</v>
+        <v>-0.53329483210807282</v>
       </c>
       <c r="V4" s="13">
         <f>[1]Model!$U$3</f>
@@ -1445,7 +1443,7 @@
       </c>
       <c r="W4" s="23">
         <f>G4/V4</f>
-        <v>4.2661678781209798</v>
+        <v>4.893287044929715</v>
       </c>
       <c r="X4" s="15">
         <f>[1]Model!T$19</f>
@@ -1469,7 +1467,7 @@
       </c>
       <c r="AC4" s="15">
         <f>[1]Model!$AH$27</f>
-        <v>-0.40653647602383658</v>
+        <v>-0.48655350922324592</v>
       </c>
       <c r="AD4" s="10" t="str">
         <f>[1]Model!$AH$28</f>
@@ -1480,7 +1478,7 @@
       </c>
       <c r="AG4" s="17">
         <f>[1]Main!$E$3</f>
-        <v>45909</v>
+        <v>45950</v>
       </c>
       <c r="AH4" s="17">
         <f>[1]Main!$G$3</f>
@@ -1496,19 +1494,19 @@
       </c>
       <c r="D5" s="12">
         <f>[2]Main!$D$3</f>
-        <v>70.709999999999994</v>
+        <v>132.12</v>
       </c>
       <c r="E5" s="13">
         <f>[2]Main!$D$5</f>
-        <v>16546.14</v>
+        <v>31246.38</v>
       </c>
       <c r="F5" s="13">
         <f>[2]Main!$D$8</f>
-        <v>-771.2</v>
+        <v>-745.59999999999991</v>
       </c>
       <c r="G5" s="13">
         <f>[2]Main!$D$9</f>
-        <v>17317.34</v>
+        <v>31991.98</v>
       </c>
       <c r="H5" s="13">
         <f>[2]Model!W$28</f>
@@ -1520,59 +1518,59 @@
       </c>
       <c r="J5" s="13">
         <f>[2]Model!Y$28</f>
-        <v>43.17933000000022</v>
+        <v>9.224400000000152</v>
       </c>
       <c r="K5" s="13">
         <f>[2]Model!Z$28</f>
-        <v>145.19444115000002</v>
+        <v>215.01444689999951</v>
       </c>
       <c r="L5" s="13">
         <f>[2]Model!AA$28</f>
-        <v>188.6412343169998</v>
+        <v>301.22465602799997</v>
       </c>
       <c r="M5" s="13">
         <f>[2]Model!AB$28</f>
-        <v>236.63731889367591</v>
+        <v>380.12981731463947</v>
       </c>
       <c r="N5" s="14">
         <f>$G5/I5</f>
-        <v>-581.11879194630376</v>
+        <v>-1073.5563758389171</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" ref="O5:R7" si="6">$G5/J5</f>
-        <v>401.05624612516942</v>
+        <v>3468.1908850439563</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="6"/>
-        <v>119.26999314050528</v>
+        <v>148.78990905610664</v>
       </c>
       <c r="Q5" s="14">
         <f t="shared" si="6"/>
-        <v>91.800395935171267</v>
+        <v>106.20637905891151</v>
       </c>
       <c r="R5" s="14">
         <f t="shared" si="6"/>
-        <v>73.18093393282949</v>
+        <v>84.160669704896449</v>
       </c>
       <c r="S5" s="21">
-        <f>G5/[2]Model!$P$83</f>
-        <v>6.8434459592965817</v>
+        <f>G5/[2]Model!$Q$65</f>
+        <v>12.126442271245548</v>
       </c>
       <c r="T5" s="15">
-        <f>[2]Model!$P$83/G5-1</f>
-        <v>-0.8538747867744122</v>
+        <f>[2]Model!$Q$65/G5-1</f>
+        <v>-0.91753558235532784</v>
       </c>
       <c r="U5" s="15">
         <f>AVERAGE(T5,AC5)</f>
-        <v>-0.84609153165335782</v>
+        <v>-0.85140914199130457</v>
       </c>
       <c r="V5" s="13">
         <f>[2]Model!$Y$7</f>
-        <v>1751.5670000000002</v>
+        <v>1976.9399999999998</v>
       </c>
       <c r="W5" s="23">
         <f t="shared" ref="W5:W8" si="7">G5/V5</f>
-        <v>9.8867699608407769</v>
+        <v>16.182575090796888</v>
       </c>
       <c r="X5" s="15">
         <f>[2]Model!X$36</f>
@@ -1580,15 +1578,15 @@
       </c>
       <c r="Y5" s="15">
         <f>[2]Model!Y$36</f>
-        <v>0.18846994164744224</v>
+        <v>0.34138960510245608</v>
       </c>
       <c r="Z5" s="15">
         <f>[2]Model!$Y$41</f>
-        <v>0.3176466158588282</v>
+        <v>0.31610691270347108</v>
       </c>
       <c r="AA5" s="15">
         <f>[2]Model!$Y$45</f>
-        <v>5.5310090907170664E-2</v>
+        <v>4.4829079284146284E-2</v>
       </c>
       <c r="AB5" s="15">
         <f>[2]Model!$AM$34</f>
@@ -1596,7 +1594,7 @@
       </c>
       <c r="AC5" s="15">
         <f>[2]Model!$AM$40</f>
-        <v>-0.83830827653230344</v>
+        <v>-0.7852827016272812</v>
       </c>
       <c r="AD5" s="10" t="str">
         <f>[2]Model!$AM$41</f>
@@ -1607,11 +1605,11 @@
       </c>
       <c r="AG5" s="17">
         <f>[2]Main!$E$3</f>
-        <v>45927</v>
+        <v>45959</v>
       </c>
       <c r="AH5" s="17">
         <f>[2]Main!$G$3</f>
-        <v>45960</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="6" spans="2:34" x14ac:dyDescent="0.3">
@@ -1623,11 +1621,11 @@
       </c>
       <c r="D6" s="12">
         <f>[3]Main!$D$3</f>
-        <v>109.4</v>
+        <v>139.09</v>
       </c>
       <c r="E6" s="13">
         <f>[3]Main!$D$5</f>
-        <v>16147.44</v>
+        <v>20529.684000000001</v>
       </c>
       <c r="F6" s="13">
         <f>[3]Main!$D$8</f>
@@ -1635,7 +1633,7 @@
       </c>
       <c r="G6" s="13">
         <f>[3]Main!$D$9</f>
-        <v>15464.44</v>
+        <v>19846.684000000001</v>
       </c>
       <c r="H6" s="13">
         <f>[3]Model!Q$17</f>
@@ -1663,35 +1661,35 @@
       </c>
       <c r="N6" s="14">
         <f>$G6/I6</f>
-        <v>-209.82957937584808</v>
+        <v>-269.29014925373139</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="6"/>
-        <v>-138.57025089605736</v>
+        <v>-177.83767025089608</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="6"/>
-        <v>-117.51094224924013</v>
+        <v>-150.81066869300912</v>
       </c>
       <c r="Q6" s="14">
         <f t="shared" si="6"/>
-        <v>-166.6067657832364</v>
+        <v>-213.81904761904764</v>
       </c>
       <c r="R6" s="14">
         <f t="shared" si="6"/>
-        <v>-464.606879975965</v>
+        <v>-596.26510440138179</v>
       </c>
       <c r="S6" s="21">
         <f>[3]Model!$L$55</f>
-        <v>21.155184678522573</v>
-      </c>
-      <c r="T6" s="24">
+        <v>27.150046511627909</v>
+      </c>
+      <c r="T6" s="15">
         <f>[3]Model!$L$56</f>
-        <v>-0.95273026375348868</v>
+        <v>-0.9631676505757838</v>
       </c>
       <c r="U6" s="15">
         <f>AVERAGE(T6,AC6)</f>
-        <v>-0.89626137950703055</v>
+        <v>-0.91857893270577462</v>
       </c>
       <c r="V6" s="18">
         <f>[3]Model!$Q$6</f>
@@ -1720,7 +1718,7 @@
       </c>
       <c r="AC6" s="15">
         <f>[3]Model!$AG$29</f>
-        <v>-0.83979249526057242</v>
+        <v>-0.87399021483576544</v>
       </c>
       <c r="AD6" s="15" t="str">
         <f>[3]Model!$AG$30</f>
@@ -1731,7 +1729,7 @@
       </c>
       <c r="AG6" s="16">
         <f>[3]Main!$E$3</f>
-        <v>45927</v>
+        <v>45939</v>
       </c>
       <c r="AH6" s="16">
         <f>[3]Main!$G$3</f>
@@ -1747,11 +1745,11 @@
       </c>
       <c r="D7" s="12">
         <f>[4]Main!$D$3</f>
-        <v>2.37</v>
+        <v>3.51</v>
       </c>
       <c r="E7" s="13">
         <f>[4]Main!$D$5</f>
-        <v>2736.8760000000002</v>
+        <v>4053.3479999999995</v>
       </c>
       <c r="F7" s="13">
         <f>[4]Main!$D$8</f>
@@ -1759,7 +1757,7 @@
       </c>
       <c r="G7" s="13">
         <f>[4]Main!$D$9</f>
-        <v>2230.5760000000005</v>
+        <v>3547.0479999999998</v>
       </c>
       <c r="H7" s="13">
         <f>[4]Model!Z$33</f>
@@ -1787,35 +1785,35 @@
       </c>
       <c r="N7" s="14">
         <f>$G7/I7</f>
-        <v>-1.0597063993538887</v>
+        <v>-1.6851384863889018</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="6"/>
-        <v>-2.4502386718082767</v>
+        <v>-3.8963542064292818</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="6"/>
-        <v>-4.3847355221088984</v>
+        <v>-6.9725789949436017</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="6"/>
-        <v>-6.3479432241156308</v>
+        <v>-10.094459600216668</v>
       </c>
       <c r="R7" s="14">
         <f t="shared" si="6"/>
-        <v>-11.634134362381594</v>
+        <v>-18.50052767617732</v>
       </c>
       <c r="S7" s="21">
         <f>G7/[4]Model!$P$93</f>
-        <v>0.6650891526030176</v>
+        <v>1.0576206094579281</v>
       </c>
       <c r="T7" s="15">
         <f>[4]Model!$P$93/G7-1</f>
-        <v>0.50355782542267091</v>
+        <v>-5.4481360274797441E-2</v>
       </c>
       <c r="U7" s="15">
         <f>AVERAGE(T7,AC7)</f>
-        <v>-0.17045299592318164</v>
+        <v>-0.47473060135215811</v>
       </c>
       <c r="V7" s="13">
         <f>[4]Model!$AB$8</f>
@@ -1823,7 +1821,7 @@
       </c>
       <c r="W7" s="23">
         <f t="shared" si="7"/>
-        <v>3.0201689774696714</v>
+        <v>4.802653812824957</v>
       </c>
       <c r="X7" s="15">
         <f>[4]Model!AA$42</f>
@@ -1847,7 +1845,7 @@
       </c>
       <c r="AC7" s="15">
         <f>[4]Model!$AP$45</f>
-        <v>-0.84446381726903419</v>
+        <v>-0.89497984242951878</v>
       </c>
       <c r="AD7" s="10" t="str">
         <f>[4]Model!$AP$46</f>
@@ -1858,7 +1856,7 @@
       </c>
       <c r="AG7" s="17">
         <f>[4]Main!$E$3</f>
-        <v>45927</v>
+        <v>45950</v>
       </c>
       <c r="AH7" s="17">
         <f>[4]Main!$G$3</f>
@@ -1874,11 +1872,11 @@
       </c>
       <c r="D8" s="12">
         <f>[5]Main!$D$3</f>
-        <v>7.85</v>
+        <v>7.81</v>
       </c>
       <c r="E8" s="13">
         <f>[5]Main!$D$5</f>
-        <v>191.54</v>
+        <v>190.56399999999999</v>
       </c>
       <c r="F8" s="13">
         <f>[5]Main!$D$8</f>
@@ -1886,7 +1884,7 @@
       </c>
       <c r="G8" s="13">
         <f>[5]Main!$D$9</f>
-        <v>90.640000000000015</v>
+        <v>89.664000000000016</v>
       </c>
       <c r="H8" s="13">
         <f>[5]Model!Y$24</f>
@@ -1914,35 +1912,35 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" ref="N8" si="8">$G8/I8</f>
-        <v>2.8866242038216563</v>
+        <v>2.8555414012738858</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8" si="9">$G8/J8</f>
-        <v>1.838539553752536</v>
+        <v>1.8187423935091283</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" ref="P8" si="10">$G8/K8</f>
-        <v>0.79300087489063886</v>
+        <v>0.78446194225721799</v>
       </c>
       <c r="Q8" s="14">
         <f t="shared" ref="Q8" si="11">$G8/L8</f>
-        <v>0.72165605095541419</v>
+        <v>0.71388535031847145</v>
       </c>
       <c r="R8" s="14">
         <f t="shared" ref="R8" si="12">$G8/M8</f>
-        <v>0.73931484502446998</v>
+        <v>0.73135399673735746</v>
       </c>
       <c r="S8" s="21">
         <f>G8/[5]Model!$AE$85</f>
-        <v>0.10912593306043825</v>
+        <v>0.10795087888273538</v>
       </c>
       <c r="T8" s="15">
         <f>[5]Model!$AE$85/G8-1</f>
-        <v>8.1637246248896727</v>
+        <v>8.2634725196288343</v>
       </c>
       <c r="U8" s="15">
         <f>AVERAGE(T8,AC8)</f>
-        <v>4.0602140921927869</v>
+        <v>4.1125379846571075</v>
       </c>
       <c r="V8" s="20">
         <f>[5]Model!$AE$13</f>
@@ -1950,7 +1948,7 @@
       </c>
       <c r="W8" s="23">
         <f t="shared" si="7"/>
-        <v>0.56607544341743699</v>
+        <v>0.55998001498875849</v>
       </c>
       <c r="X8" s="15">
         <f>[5]Model!$AD$45</f>
@@ -1974,7 +1972,7 @@
       </c>
       <c r="AC8" s="15">
         <f>[5]Model!$AS$129</f>
-        <v>-4.329644050409831E-2</v>
+        <v>-3.8396550314618638E-2</v>
       </c>
       <c r="AD8" s="10" t="str">
         <f>[5]Model!$AS$130</f>
@@ -1985,11 +1983,11 @@
       </c>
       <c r="AG8" s="16">
         <f>[5]Main!$E$3</f>
-        <v>45927</v>
+        <v>45959</v>
       </c>
       <c r="AH8" s="16">
         <f>[5]Main!$G$3</f>
-        <v>45912</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.3">

--- a/Financial Analysis/Models (Energy).xlsx
+++ b/Financial Analysis/Models (Energy).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B352EE1-D63D-44E7-A34A-0B905A3D8257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558AEF1A-1D55-4825-B61B-A4F84E5BDE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{14D7A11B-4B63-41BA-92AC-B31B19EF0AA6}"/>
   </bookViews>
@@ -655,35 +655,35 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>3.51</v>
+            <v>2.46</v>
           </cell>
           <cell r="E3">
-            <v>45950</v>
+            <v>45975</v>
           </cell>
           <cell r="G3">
-            <v>45972</v>
+            <v>46079</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>4053.3479999999995</v>
+            <v>3422.8440000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>506.29999999999973</v>
+            <v>215.39999999999998</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3547.0479999999998</v>
+            <v>3207.444</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="8">
           <cell r="AB8">
-            <v>738.56</v>
+            <v>722.06</v>
           </cell>
         </row>
         <row r="33">
@@ -694,16 +694,16 @@
             <v>-2104.9</v>
           </cell>
           <cell r="AB33">
-            <v>-910.35050000000001</v>
+            <v>-1049.8714999999997</v>
           </cell>
           <cell r="AC33">
-            <v>-508.71392100000014</v>
+            <v>-504.67788450000006</v>
           </cell>
           <cell r="AD33">
-            <v>-351.38562542999983</v>
+            <v>-346.54102523999978</v>
           </cell>
           <cell r="AE33">
-            <v>-191.72685569219993</v>
+            <v>-189.44181374939978</v>
           </cell>
         </row>
         <row r="39">
@@ -716,12 +716,12 @@
             <v>-0.29443447037701986</v>
           </cell>
           <cell r="AB42">
-            <v>0.17455470737913492</v>
+            <v>0.14831424936386761</v>
           </cell>
         </row>
         <row r="45">
           <cell r="AP45">
-            <v>-0.89497984242951878</v>
+            <v>-0.96385102391432786</v>
           </cell>
         </row>
         <row r="46">
@@ -731,12 +731,12 @@
         </row>
         <row r="48">
           <cell r="AB48">
-            <v>-0.44518996425476615</v>
+            <v>-0.49127150098329775</v>
           </cell>
         </row>
         <row r="51">
           <cell r="AB51">
-            <v>-1.0778413399046796</v>
+            <v>-1.3056691964656677</v>
           </cell>
         </row>
         <row r="93">
@@ -764,92 +764,92 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>7.81</v>
+            <v>8.34</v>
           </cell>
           <cell r="E3">
-            <v>45959</v>
+            <v>46012</v>
           </cell>
           <cell r="G3">
-            <v>46009</v>
+            <v>46091</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>190.56399999999999</v>
+            <v>397.81800000000004</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>100.89999999999998</v>
+            <v>210.80000000000007</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>89.664000000000016</v>
+            <v>187.01799999999997</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="13">
-          <cell r="AE13">
-            <v>160.12</v>
+          <cell r="AI13">
+            <v>158</v>
           </cell>
         </row>
         <row r="24">
-          <cell r="Y24">
+          <cell r="AC24">
             <v>45.7</v>
           </cell>
-          <cell r="Z24">
+          <cell r="AD24">
             <v>31.400000000000002</v>
           </cell>
-          <cell r="AA24">
+          <cell r="AE24">
             <v>49.3</v>
           </cell>
-          <cell r="AB24">
+          <cell r="AF24">
             <v>114.3</v>
           </cell>
-          <cell r="AC24">
+          <cell r="AG24">
             <v>125.6</v>
           </cell>
-          <cell r="AD24">
+          <cell r="AH24">
             <v>122.6</v>
           </cell>
         </row>
         <row r="43">
-          <cell r="AS43">
+          <cell r="AW43">
             <v>0.12</v>
           </cell>
         </row>
         <row r="45">
-          <cell r="AD45">
+          <cell r="AH45">
             <v>-9.0761750405186525E-2</v>
           </cell>
-          <cell r="AE45">
-            <v>0.4270944741532976</v>
+          <cell r="AI45">
+            <v>0.40819964349376114</v>
           </cell>
         </row>
         <row r="50">
-          <cell r="AE50">
-            <v>-0.15485885585810655</v>
+          <cell r="AI50">
+            <v>-0.16835443037974679</v>
           </cell>
         </row>
         <row r="53">
-          <cell r="AE53">
-            <v>-1.2246814888833375</v>
+          <cell r="AI53">
+            <v>-1.218987341772152</v>
           </cell>
         </row>
         <row r="85">
-          <cell r="AE85">
+          <cell r="AI85">
             <v>830.6</v>
           </cell>
         </row>
         <row r="129">
-          <cell r="AS129">
-            <v>-3.8396550314618638E-2</v>
+          <cell r="AW129">
+            <v>-0.10952164578557977</v>
           </cell>
         </row>
         <row r="130">
-          <cell r="AS130" t="str">
+          <cell r="AW130" t="str">
             <v>Fairly valued</v>
           </cell>
         </row>
@@ -1296,23 +1296,23 @@
       <c r="M3" s="2"/>
       <c r="N3" s="6">
         <f>TRIMMEAN(N4:N1048576,80%)</f>
-        <v>-1.6851384863889018</v>
+        <v>-1.5237987552852865</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" ref="O3:R3" si="0">TRIMMEAN(O4:O1048576,80%)</f>
-        <v>1.8187423935091283</v>
+        <v>3.793468559837728</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>0.78446194225721799</v>
+        <v>1.6362029746281712</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>0.71388535031847145</v>
+        <v>1.488996815286624</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>0.73135399673735746</v>
+        <v>1.525432300163132</v>
       </c>
       <c r="S3" s="22">
         <f>TRIMMEAN(S4:S1048576,80%)</f>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Y3" s="8">
         <f t="shared" si="1"/>
-        <v>0.17455470737913492</v>
+        <v>0.14831424936386761</v>
       </c>
       <c r="Z3" s="8">
         <f t="shared" si="1"/>
@@ -1745,19 +1745,19 @@
       </c>
       <c r="D7" s="12">
         <f>[4]Main!$D$3</f>
-        <v>3.51</v>
+        <v>2.46</v>
       </c>
       <c r="E7" s="13">
         <f>[4]Main!$D$5</f>
-        <v>4053.3479999999995</v>
+        <v>3422.8440000000001</v>
       </c>
       <c r="F7" s="13">
         <f>[4]Main!$D$8</f>
-        <v>506.29999999999973</v>
+        <v>215.39999999999998</v>
       </c>
       <c r="G7" s="13">
         <f>[4]Main!$D$9</f>
-        <v>3547.0479999999998</v>
+        <v>3207.444</v>
       </c>
       <c r="H7" s="13">
         <f>[4]Model!Z$33</f>
@@ -1769,59 +1769,59 @@
       </c>
       <c r="J7" s="13">
         <f>[4]Model!AB$33</f>
-        <v>-910.35050000000001</v>
+        <v>-1049.8714999999997</v>
       </c>
       <c r="K7" s="13">
         <f>[4]Model!AC$33</f>
-        <v>-508.71392100000014</v>
+        <v>-504.67788450000006</v>
       </c>
       <c r="L7" s="13">
         <f>[4]Model!AD$33</f>
-        <v>-351.38562542999983</v>
+        <v>-346.54102523999978</v>
       </c>
       <c r="M7" s="13">
         <f>[4]Model!AE$33</f>
-        <v>-191.72685569219993</v>
+        <v>-189.44181374939978</v>
       </c>
       <c r="N7" s="14">
         <f>$G7/I7</f>
-        <v>-1.6851384863889018</v>
+        <v>-1.5237987552852865</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="6"/>
-        <v>-3.8963542064292818</v>
+        <v>-3.0550824553290576</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="6"/>
-        <v>-6.9725789949436017</v>
+        <v>-6.3554280829597154</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="6"/>
-        <v>-10.094459600216668</v>
+        <v>-9.2555967876491927</v>
       </c>
       <c r="R7" s="14">
         <f t="shared" si="6"/>
-        <v>-18.50052767617732</v>
+        <v>-16.931024553232575</v>
       </c>
       <c r="S7" s="21">
         <f>G7/[4]Model!$P$93</f>
-        <v>1.0576206094579281</v>
+        <v>0.95636114258453087</v>
       </c>
       <c r="T7" s="15">
         <f>[4]Model!$P$93/G7-1</f>
-        <v>-5.4481360274797441E-2</v>
+        <v>4.563010297295933E-2</v>
       </c>
       <c r="U7" s="15">
         <f>AVERAGE(T7,AC7)</f>
-        <v>-0.47473060135215811</v>
+        <v>-0.45911046047068427</v>
       </c>
       <c r="V7" s="13">
         <f>[4]Model!$AB$8</f>
-        <v>738.56</v>
+        <v>722.06</v>
       </c>
       <c r="W7" s="23">
         <f t="shared" si="7"/>
-        <v>4.802653812824957</v>
+        <v>4.4420740658671027</v>
       </c>
       <c r="X7" s="15">
         <f>[4]Model!AA$42</f>
@@ -1829,15 +1829,15 @@
       </c>
       <c r="Y7" s="15">
         <f>[4]Model!AB$42</f>
-        <v>0.17455470737913492</v>
+        <v>0.14831424936386761</v>
       </c>
       <c r="Z7" s="15">
         <f>[4]Model!$AB$48</f>
-        <v>-0.44518996425476615</v>
+        <v>-0.49127150098329775</v>
       </c>
       <c r="AA7" s="15">
         <f>[4]Model!$AB$51</f>
-        <v>-1.0778413399046796</v>
+        <v>-1.3056691964656677</v>
       </c>
       <c r="AB7" s="15">
         <f>[4]Model!$AP$39</f>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC7" s="15">
         <f>[4]Model!$AP$45</f>
-        <v>-0.89497984242951878</v>
+        <v>-0.96385102391432786</v>
       </c>
       <c r="AD7" s="10" t="str">
         <f>[4]Model!$AP$46</f>
@@ -1856,11 +1856,11 @@
       </c>
       <c r="AG7" s="17">
         <f>[4]Main!$E$3</f>
-        <v>45950</v>
+        <v>45975</v>
       </c>
       <c r="AH7" s="17">
         <f>[4]Main!$G$3</f>
-        <v>45972</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.3">
@@ -1872,110 +1872,110 @@
       </c>
       <c r="D8" s="12">
         <f>[5]Main!$D$3</f>
-        <v>7.81</v>
+        <v>8.34</v>
       </c>
       <c r="E8" s="13">
         <f>[5]Main!$D$5</f>
-        <v>190.56399999999999</v>
+        <v>397.81800000000004</v>
       </c>
       <c r="F8" s="13">
         <f>[5]Main!$D$8</f>
-        <v>100.89999999999998</v>
+        <v>210.80000000000007</v>
       </c>
       <c r="G8" s="13">
         <f>[5]Main!$D$9</f>
-        <v>89.664000000000016</v>
+        <v>187.01799999999997</v>
       </c>
       <c r="H8" s="13">
-        <f>[5]Model!Y$24</f>
+        <f>[5]Model!AC$24</f>
         <v>45.7</v>
       </c>
       <c r="I8" s="13">
-        <f>[5]Model!Z$24</f>
+        <f>[5]Model!AD$24</f>
         <v>31.400000000000002</v>
       </c>
       <c r="J8" s="13">
-        <f>[5]Model!AA$24</f>
+        <f>[5]Model!AE$24</f>
         <v>49.3</v>
       </c>
       <c r="K8" s="13">
-        <f>[5]Model!AB$24</f>
+        <f>[5]Model!AF$24</f>
         <v>114.3</v>
       </c>
       <c r="L8" s="13">
-        <f>[5]Model!AC$24</f>
+        <f>[5]Model!AG$24</f>
         <v>125.6</v>
       </c>
       <c r="M8" s="13">
-        <f>[5]Model!AD$24</f>
+        <f>[5]Model!AH$24</f>
         <v>122.6</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" ref="N8" si="8">$G8/I8</f>
-        <v>2.8555414012738858</v>
+        <v>5.9559872611464959</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8" si="9">$G8/J8</f>
-        <v>1.8187423935091283</v>
+        <v>3.793468559837728</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" ref="P8" si="10">$G8/K8</f>
-        <v>0.78446194225721799</v>
+        <v>1.6362029746281712</v>
       </c>
       <c r="Q8" s="14">
         <f t="shared" ref="Q8" si="11">$G8/L8</f>
-        <v>0.71388535031847145</v>
+        <v>1.488996815286624</v>
       </c>
       <c r="R8" s="14">
         <f t="shared" ref="R8" si="12">$G8/M8</f>
-        <v>0.73135399673735746</v>
+        <v>1.525432300163132</v>
       </c>
       <c r="S8" s="21">
-        <f>G8/[5]Model!$AE$85</f>
-        <v>0.10795087888273538</v>
+        <f>G8/[5]Model!$AI$85</f>
+        <v>0.22516012521069104</v>
       </c>
       <c r="T8" s="15">
-        <f>[5]Model!$AE$85/G8-1</f>
-        <v>8.2634725196288343</v>
+        <f>[5]Model!$AI$85/G8-1</f>
+        <v>3.4412837267001049</v>
       </c>
       <c r="U8" s="15">
         <f>AVERAGE(T8,AC8)</f>
-        <v>4.1125379846571075</v>
+        <v>1.6658810404572626</v>
       </c>
       <c r="V8" s="20">
-        <f>[5]Model!$AE$13</f>
-        <v>160.12</v>
+        <f>[5]Model!$AI$13</f>
+        <v>158</v>
       </c>
       <c r="W8" s="23">
         <f t="shared" si="7"/>
-        <v>0.55998001498875849</v>
+        <v>1.1836582278481012</v>
       </c>
       <c r="X8" s="15">
-        <f>[5]Model!$AD$45</f>
+        <f>[5]Model!$AH$45</f>
         <v>-9.0761750405186525E-2</v>
       </c>
       <c r="Y8" s="15">
-        <f>[5]Model!$AE$45</f>
-        <v>0.4270944741532976</v>
+        <f>[5]Model!$AI$45</f>
+        <v>0.40819964349376114</v>
       </c>
       <c r="Z8" s="15">
-        <f>[5]Model!$AE$50</f>
-        <v>-0.15485885585810655</v>
+        <f>[5]Model!$AI$50</f>
+        <v>-0.16835443037974679</v>
       </c>
       <c r="AA8" s="15">
-        <f>[5]Model!$AE$53</f>
-        <v>-1.2246814888833375</v>
+        <f>[5]Model!$AI$53</f>
+        <v>-1.218987341772152</v>
       </c>
       <c r="AB8" s="15">
-        <f>[5]Model!$AS$43</f>
+        <f>[5]Model!$AW$43</f>
         <v>0.12</v>
       </c>
       <c r="AC8" s="15">
-        <f>[5]Model!$AS$129</f>
-        <v>-3.8396550314618638E-2</v>
+        <f>[5]Model!$AW$129</f>
+        <v>-0.10952164578557977</v>
       </c>
       <c r="AD8" s="10" t="str">
-        <f>[5]Model!$AS$130</f>
+        <f>[5]Model!$AW$130</f>
         <v>Fairly valued</v>
       </c>
       <c r="AE8" s="10">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="AG8" s="16">
         <f>[5]Main!$E$3</f>
-        <v>45959</v>
+        <v>46012</v>
       </c>
       <c r="AH8" s="16">
         <f>[5]Main!$G$3</f>
-        <v>46009</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.3">

--- a/Financial Analysis/Models (Energy).xlsx
+++ b/Financial Analysis/Models (Energy).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558AEF1A-1D55-4825-B61B-A4F84E5BDE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9936F14D-8F12-430C-BB58-C615FFED205D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{14D7A11B-4B63-41BA-92AC-B31B19EF0AA6}"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Company</t>
   </si>
@@ -167,6 +168,18 @@
   </si>
   <si>
     <t>2025 EV/R</t>
+  </si>
+  <si>
+    <t>Enphase</t>
+  </si>
+  <si>
+    <t>ENPH US</t>
+  </si>
+  <si>
+    <t>General Electric</t>
+  </si>
+  <si>
+    <t>GEV US</t>
   </si>
 </sst>
 </file>
@@ -252,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -315,6 +328,9 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -347,87 +363,87 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>384.26</v>
+            <v>312.64</v>
           </cell>
           <cell r="E3">
-            <v>45950</v>
+            <v>46078</v>
           </cell>
           <cell r="G3">
-            <v>45971</v>
+            <v>46149</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>120042.82399999999</v>
+            <v>97637.471999999994</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-6249</v>
+            <v>-5244</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>126291.82399999999</v>
+            <v>102881.47199999999</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="U3">
-            <v>25809.200000000001</v>
+          <cell r="X3">
+            <v>25533</v>
           </cell>
         </row>
         <row r="15">
-          <cell r="S15">
+          <cell r="V15">
             <v>1588</v>
           </cell>
-          <cell r="T15">
+          <cell r="W15">
             <v>3742</v>
           </cell>
-          <cell r="U15">
-            <v>2203.3357160000005</v>
-          </cell>
-          <cell r="V15">
-            <v>3891.0411407519982</v>
-          </cell>
-          <cell r="W15">
-            <v>4232.0017609521583</v>
-          </cell>
           <cell r="X15">
-            <v>4507.3319396302886</v>
+            <v>2324</v>
+          </cell>
+          <cell r="Y15">
+            <v>3469.3330688000005</v>
+          </cell>
+          <cell r="Z15">
+            <v>3776.8657053040024</v>
+          </cell>
+          <cell r="AA15">
+            <v>4025.1103982722416</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="T19">
+          <cell r="W19">
             <v>-5.4177702865398469E-2</v>
           </cell>
-          <cell r="U19">
-            <v>9.5095044127630812E-2</v>
+          <cell r="X19">
+            <v>8.3375763747454146E-2</v>
           </cell>
         </row>
         <row r="21">
-          <cell r="AH21">
+          <cell r="AK21">
             <v>7.0000000000000007E-2</v>
           </cell>
         </row>
         <row r="22">
-          <cell r="U22">
-            <v>0.18578801357655411</v>
+          <cell r="X22">
+            <v>0.18380135510907453</v>
           </cell>
         </row>
         <row r="23">
-          <cell r="U23">
-            <v>0.12163589727694003</v>
+          <cell r="X23">
+            <v>0.12086319664747582</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AH27">
-            <v>-0.48655350922324592</v>
+          <cell r="AK27">
+            <v>-0.42864786747104966</v>
           </cell>
         </row>
         <row r="28">
-          <cell r="AH28" t="str">
+          <cell r="AK28" t="str">
             <v>Overvalued</v>
           </cell>
         </row>
@@ -456,91 +472,91 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>132.12</v>
+            <v>147.55000000000001</v>
           </cell>
           <cell r="E3">
-            <v>45959</v>
+            <v>46076</v>
           </cell>
           <cell r="G3">
-            <v>46058</v>
+            <v>46148</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>31246.38</v>
+            <v>41387.775000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-745.59999999999991</v>
+            <v>-407.59999999999991</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>31991.98</v>
+            <v>41795.375</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="7">
-          <cell r="Y7">
-            <v>1976.9399999999998</v>
+          <cell r="AC7">
+            <v>2024.1000000000001</v>
           </cell>
         </row>
         <row r="28">
-          <cell r="W28">
+          <cell r="AA28">
             <v>-302.29999999999995</v>
           </cell>
-          <cell r="X28">
+          <cell r="AB28">
             <v>-29.800000000000253</v>
           </cell>
-          <cell r="Y28">
-            <v>9.224400000000152</v>
-          </cell>
-          <cell r="Z28">
-            <v>215.01444689999951</v>
-          </cell>
-          <cell r="AA28">
-            <v>301.22465602799997</v>
-          </cell>
-          <cell r="AB28">
-            <v>380.12981731463947</v>
+          <cell r="AC28">
+            <v>-87.799999999999912</v>
+          </cell>
+          <cell r="AD28">
+            <v>361.31132399999984</v>
+          </cell>
+          <cell r="AE28">
+            <v>564.98599631999946</v>
+          </cell>
+          <cell r="AF28">
+            <v>693.81725338200022</v>
           </cell>
         </row>
         <row r="34">
-          <cell r="AM34">
-            <v>0.09</v>
+          <cell r="AQ34">
+            <v>0.08</v>
           </cell>
         </row>
         <row r="36">
-          <cell r="X36">
+          <cell r="AB36">
             <v>0.10537763444086101</v>
           </cell>
-          <cell r="Y36">
-            <v>0.34138960510245608</v>
+          <cell r="AC36">
+            <v>0.37338851947347007</v>
           </cell>
         </row>
         <row r="40">
-          <cell r="AM40">
-            <v>-0.7852827016272812</v>
+          <cell r="AQ40">
+            <v>-0.65424051466376831</v>
           </cell>
         </row>
         <row r="41">
-          <cell r="Y41">
-            <v>0.31610691270347108</v>
-          </cell>
-          <cell r="AM41" t="str">
+          <cell r="AC41">
+            <v>0.29030186255619789</v>
+          </cell>
+          <cell r="AQ41" t="str">
             <v>Heavily overvalued</v>
           </cell>
         </row>
         <row r="45">
-          <cell r="Y45">
-            <v>4.4829079284146284E-2</v>
+          <cell r="AC45">
+            <v>3.6016007114273052E-2</v>
           </cell>
         </row>
         <row r="65">
-          <cell r="Q65">
-            <v>2638.2</v>
+          <cell r="R65">
+            <v>4396.7</v>
           </cell>
         </row>
       </sheetData>
@@ -563,28 +579,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>139.09</v>
+            <v>63.83</v>
           </cell>
           <cell r="E3">
-            <v>45939</v>
+            <v>46076</v>
           </cell>
           <cell r="G3">
-            <v>45988</v>
+            <v>46077</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>20529.684000000001</v>
+            <v>9970.2459999999992</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>683</v>
+            <v>1183.5999999999999</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>19846.684000000001</v>
+            <v>8786.6459999999988</v>
           </cell>
         </row>
       </sheetData>
@@ -617,7 +633,7 @@
         </row>
         <row r="29">
           <cell r="AG29">
-            <v>-0.87399021483576544</v>
+            <v>-0.69032448443803462</v>
           </cell>
         </row>
         <row r="30">
@@ -627,12 +643,12 @@
         </row>
         <row r="55">
           <cell r="L55">
-            <v>27.150046511627909</v>
+            <v>12.020035567715457</v>
           </cell>
         </row>
         <row r="56">
           <cell r="L56">
-            <v>-0.9631676505757838</v>
+            <v>-0.91680557063525714</v>
           </cell>
         </row>
       </sheetData>
@@ -655,93 +671,88 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>2.46</v>
+            <v>49.74</v>
           </cell>
           <cell r="E3">
-            <v>45975</v>
+            <v>46078</v>
           </cell>
           <cell r="G3">
-            <v>46079</v>
+            <v>46140</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>3422.8440000000001</v>
+            <v>6510.9660000000003</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>215.39999999999998</v>
+            <v>274.30000000000018</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3207.444</v>
+            <v>6236.6660000000002</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="8">
-          <cell r="AB8">
-            <v>722.06</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="Z33">
-            <v>-1368.8</v>
-          </cell>
-          <cell r="AA33">
-            <v>-2104.9</v>
-          </cell>
-          <cell r="AB33">
-            <v>-1049.8714999999997</v>
-          </cell>
-          <cell r="AC33">
-            <v>-504.67788450000006</v>
-          </cell>
-          <cell r="AD33">
-            <v>-346.54102523999978</v>
-          </cell>
-          <cell r="AE33">
-            <v>-189.44181374939978</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="AP39">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="AA42">
-            <v>-0.29443447037701986</v>
-          </cell>
-          <cell r="AB42">
-            <v>0.14831424936386761</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="AP45">
-            <v>-0.96385102391432786</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="AP46" t="str">
+        <row r="3">
+          <cell r="V3">
+            <v>1473</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="T18">
+            <v>438.99999999999994</v>
+          </cell>
+          <cell r="U18">
+            <v>102.69999999999995</v>
+          </cell>
+          <cell r="V18">
+            <v>172.09999999999991</v>
+          </cell>
+          <cell r="W18">
+            <v>227.48592500000004</v>
+          </cell>
+          <cell r="X18">
+            <v>242.79734049999996</v>
+          </cell>
+          <cell r="Y18">
+            <v>254.01334320499996</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="U22">
+            <v>-0.41924218613584774</v>
+          </cell>
+          <cell r="V22">
+            <v>0.1071858087793145</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="V23">
+            <v>0.4663951120162933</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="AI24">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="V27">
+            <v>0.10692464358452131</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AI30">
+            <v>-0.50227926621940466</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AI31" t="str">
             <v>Heavily overvalued</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="AB48">
-            <v>-0.49127150098329775</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="AB51">
-            <v>-1.3056691964656677</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="P93">
-            <v>3353.8</v>
           </cell>
         </row>
       </sheetData>
@@ -764,6 +775,115 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
+            <v>1.87</v>
+          </cell>
+          <cell r="E3">
+            <v>46076</v>
+          </cell>
+          <cell r="G3">
+            <v>46079</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>2601.9180000000001</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>215.39999999999998</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>2386.518</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="8">
+          <cell r="AB8">
+            <v>722.06</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Z33">
+            <v>-1368.8</v>
+          </cell>
+          <cell r="AA33">
+            <v>-2104.9</v>
+          </cell>
+          <cell r="AB33">
+            <v>-1049.8714999999997</v>
+          </cell>
+          <cell r="AC33">
+            <v>-504.67788450000006</v>
+          </cell>
+          <cell r="AD33">
+            <v>-346.54102523999978</v>
+          </cell>
+          <cell r="AE33">
+            <v>-189.44181374939978</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="AP39">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="AA42">
+            <v>-0.29443447037701986</v>
+          </cell>
+          <cell r="AB42">
+            <v>0.14831424936386761</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AP45">
+            <v>-0.89566878315942533</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="AP46" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="AB48">
+            <v>-0.49127150098329775</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="AB51">
+            <v>-1.3056691964656677</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="P93">
+            <v>3353.8</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
             <v>8.34</v>
           </cell>
           <cell r="E3">
@@ -791,6 +911,9 @@
       </sheetData>
       <sheetData sheetId="1">
         <row r="13">
+          <cell r="AE13">
+            <v>69.5</v>
+          </cell>
           <cell r="AI13">
             <v>158</v>
           </cell>
@@ -845,12 +968,12 @@
         </row>
         <row r="129">
           <cell r="AW129">
-            <v>-0.10952164578557977</v>
+            <v>0.25248761008022935</v>
           </cell>
         </row>
         <row r="130">
           <cell r="AW130" t="str">
-            <v>Fairly valued</v>
+            <v>Slightly undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1156,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F50123-7912-4358-B5CC-BC69536C3F1F}">
-  <dimension ref="B2:AH9"/>
+  <dimension ref="B2:AH11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
@@ -1295,65 +1418,68 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="6">
-        <f>TRIMMEAN(N4:N1048576,80%)</f>
-        <v>-1.5237987552852865</v>
+        <f t="shared" ref="N3:U3" si="0">TRIMMEAN(N4:N1048576,80%)</f>
+        <v>2.4110978160452419</v>
       </c>
       <c r="O3" s="6">
-        <f t="shared" ref="O3:R3" si="0">TRIMMEAN(O4:O1048576,80%)</f>
-        <v>3.793468559837728</v>
+        <f t="shared" si="0"/>
+        <v>0.76015804177924373</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>1.6362029746281712</v>
+        <v>14.525907805441239</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>1.488996815286624</v>
+        <v>13.587855726048538</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>1.525432300163132</v>
+        <v>13.038972824847537</v>
       </c>
       <c r="S3" s="22">
-        <f>TRIMMEAN(S4:S1048576,80%)</f>
-        <v>2.381157358874769</v>
+        <f t="shared" si="0"/>
+        <v>1.9397690712319469</v>
       </c>
       <c r="T3" s="8">
-        <f>TRIMMEAN(T4:T1048576,80%)</f>
-        <v>-0.58003615499289962</v>
+        <f t="shared" si="0"/>
+        <v>-0.48447471669145636</v>
       </c>
       <c r="U3" s="8">
-        <f>TRIMMEAN(U4:U1048576,80%)</f>
-        <v>-0.53329483210807282</v>
+        <f t="shared" si="0"/>
+        <v>-0.45656129208125301</v>
       </c>
       <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
+      <c r="W3" s="24">
+        <f t="shared" ref="W3:AC3" si="1">TRIMMEAN(W4:W1048576,80%)</f>
+        <v>4.0293530724944189</v>
+      </c>
       <c r="X3" s="8">
-        <f t="shared" ref="X3:AC3" si="1">TRIMMEAN(X4:X1048576,80%)</f>
-        <v>-5.4177702865398469E-2</v>
+        <f t="shared" si="1"/>
+        <v>-7.2469726635292497E-2</v>
       </c>
       <c r="Y3" s="8">
         <f t="shared" si="1"/>
-        <v>0.14831424936386761</v>
+        <v>0.12775002907159105</v>
       </c>
       <c r="Z3" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.1900677554537263E-2</v>
       </c>
       <c r="AA3" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.8008003557136526E-2</v>
       </c>
       <c r="AB3" s="8">
         <f t="shared" si="1"/>
-        <v>0.09</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="AC3" s="8">
         <f t="shared" si="1"/>
-        <v>-0.7852827016272812</v>
+        <v>-0.57825989044158654</v>
       </c>
       <c r="AD3" s="9" t="str">
-        <f>INDEX(AD4:AD8,MODE(MATCH(AD4:AD8,AD4:AD8,0)))</f>
+        <f>INDEX(AD4:AD9,MODE(MATCH(AD4:AD9,AD4:AD9,0)))</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AE3" s="10"/>
@@ -1367,110 +1493,110 @@
       </c>
       <c r="D4" s="12">
         <f>[1]Main!$D$3</f>
-        <v>384.26</v>
+        <v>312.64</v>
       </c>
       <c r="E4" s="13">
         <f>[1]Main!$D$5</f>
-        <v>120042.82399999999</v>
+        <v>97637.471999999994</v>
       </c>
       <c r="F4" s="13">
         <f>[1]Main!$D$8</f>
-        <v>-6249</v>
+        <v>-5244</v>
       </c>
       <c r="G4" s="13">
         <f>[1]Main!$D$9</f>
-        <v>126291.82399999999</v>
+        <v>102881.47199999999</v>
       </c>
       <c r="H4" s="13">
-        <f>[1]Model!S$15</f>
+        <f>[1]Model!V$15</f>
         <v>1588</v>
       </c>
       <c r="I4" s="13">
-        <f>[1]Model!T$15</f>
+        <f>[1]Model!W$15</f>
         <v>3742</v>
       </c>
       <c r="J4" s="13">
-        <f>[1]Model!U$15</f>
-        <v>2203.3357160000005</v>
+        <f>[1]Model!X$15</f>
+        <v>2324</v>
       </c>
       <c r="K4" s="13">
-        <f>[1]Model!V$15</f>
-        <v>3891.0411407519982</v>
+        <f>[1]Model!Y$15</f>
+        <v>3469.3330688000005</v>
       </c>
       <c r="L4" s="13">
-        <f>[1]Model!W$15</f>
-        <v>4232.0017609521583</v>
+        <f>[1]Model!Z$15</f>
+        <v>3776.8657053040024</v>
       </c>
       <c r="M4" s="13">
-        <f>[1]Model!X$15</f>
-        <v>4507.3319396302886</v>
+        <f>[1]Model!AA$15</f>
+        <v>4025.1103982722416</v>
       </c>
       <c r="N4" s="14">
         <f>$G4/I4</f>
-        <v>33.749819347942278</v>
+        <v>27.493712453233563</v>
       </c>
       <c r="O4" s="14">
         <f t="shared" ref="O4" si="2">$G4/J4</f>
-        <v>57.318466306747766</v>
+        <v>44.269135972461271</v>
       </c>
       <c r="P4" s="14">
         <f t="shared" ref="P4" si="3">$G4/K4</f>
-        <v>32.457077535703547</v>
+        <v>29.654538771506715</v>
       </c>
       <c r="Q4" s="14">
         <f t="shared" ref="Q4" si="4">$G4/L4</f>
-        <v>29.842101004132282</v>
+        <v>27.239907380217268</v>
       </c>
       <c r="R4" s="14">
         <f t="shared" ref="R4" si="5">$G4/M4</f>
-        <v>28.019197541142045</v>
+        <v>25.559913100560259</v>
       </c>
       <c r="S4" s="21">
         <f>G4/[1]Model!$L$42</f>
-        <v>2.381157358874769</v>
+        <v>1.9397690712319469</v>
       </c>
       <c r="T4" s="15">
         <f>[1]Model!$L$42/G4-1</f>
-        <v>-0.58003615499289962</v>
+        <v>-0.48447471669145636</v>
       </c>
       <c r="U4" s="15">
         <f>AVERAGE(T4,AC4)</f>
-        <v>-0.53329483210807282</v>
+        <v>-0.45656129208125301</v>
       </c>
       <c r="V4" s="13">
-        <f>[1]Model!$U$3</f>
-        <v>25809.200000000001</v>
+        <f>[1]Model!$X$3</f>
+        <v>25533</v>
       </c>
       <c r="W4" s="23">
         <f>G4/V4</f>
-        <v>4.893287044929715</v>
+        <v>4.0293530724944189</v>
       </c>
       <c r="X4" s="15">
-        <f>[1]Model!T$19</f>
+        <f>[1]Model!W$19</f>
         <v>-5.4177702865398469E-2</v>
       </c>
       <c r="Y4" s="15">
-        <f>[1]Model!U$19</f>
-        <v>9.5095044127630812E-2</v>
+        <f>[1]Model!X$19</f>
+        <v>8.3375763747454146E-2</v>
       </c>
       <c r="Z4" s="15">
-        <f>[1]Model!$U$22</f>
-        <v>0.18578801357655411</v>
+        <f>[1]Model!$X$22</f>
+        <v>0.18380135510907453</v>
       </c>
       <c r="AA4" s="15">
-        <f>[1]Model!$U$23</f>
-        <v>0.12163589727694003</v>
+        <f>[1]Model!$X$23</f>
+        <v>0.12086319664747582</v>
       </c>
       <c r="AB4" s="15">
-        <f>[1]Model!$AH$21</f>
+        <f>[1]Model!$AK$21</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AC4" s="15">
-        <f>[1]Model!$AH$27</f>
-        <v>-0.48655350922324592</v>
+        <f>[1]Model!$AK$27</f>
+        <v>-0.42864786747104966</v>
       </c>
       <c r="AD4" s="10" t="str">
-        <f>[1]Model!$AH$28</f>
+        <f>[1]Model!$AK$28</f>
         <v>Overvalued</v>
       </c>
       <c r="AE4" s="10">
@@ -1478,11 +1604,11 @@
       </c>
       <c r="AG4" s="17">
         <f>[1]Main!$E$3</f>
-        <v>45950</v>
+        <v>46078</v>
       </c>
       <c r="AH4" s="17">
         <f>[1]Main!$G$3</f>
-        <v>45971</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.3">
@@ -1494,110 +1620,110 @@
       </c>
       <c r="D5" s="12">
         <f>[2]Main!$D$3</f>
-        <v>132.12</v>
+        <v>147.55000000000001</v>
       </c>
       <c r="E5" s="13">
         <f>[2]Main!$D$5</f>
-        <v>31246.38</v>
+        <v>41387.775000000001</v>
       </c>
       <c r="F5" s="13">
         <f>[2]Main!$D$8</f>
-        <v>-745.59999999999991</v>
+        <v>-407.59999999999991</v>
       </c>
       <c r="G5" s="13">
         <f>[2]Main!$D$9</f>
-        <v>31991.98</v>
+        <v>41795.375</v>
       </c>
       <c r="H5" s="13">
-        <f>[2]Model!W$28</f>
+        <f>[2]Model!AA$28</f>
         <v>-302.29999999999995</v>
       </c>
       <c r="I5" s="13">
-        <f>[2]Model!X$28</f>
+        <f>[2]Model!AB$28</f>
         <v>-29.800000000000253</v>
       </c>
       <c r="J5" s="13">
-        <f>[2]Model!Y$28</f>
-        <v>9.224400000000152</v>
+        <f>[2]Model!AC$28</f>
+        <v>-87.799999999999912</v>
       </c>
       <c r="K5" s="13">
-        <f>[2]Model!Z$28</f>
-        <v>215.01444689999951</v>
+        <f>[2]Model!AD$28</f>
+        <v>361.31132399999984</v>
       </c>
       <c r="L5" s="13">
-        <f>[2]Model!AA$28</f>
-        <v>301.22465602799997</v>
+        <f>[2]Model!AE$28</f>
+        <v>564.98599631999946</v>
       </c>
       <c r="M5" s="13">
-        <f>[2]Model!AB$28</f>
-        <v>380.12981731463947</v>
+        <f>[2]Model!AF$28</f>
+        <v>693.81725338200022</v>
       </c>
       <c r="N5" s="14">
         <f>$G5/I5</f>
-        <v>-1073.5563758389171</v>
+        <v>-1402.5293624160954</v>
       </c>
       <c r="O5" s="14">
-        <f t="shared" ref="O5:R7" si="6">$G5/J5</f>
-        <v>3468.1908850439563</v>
+        <f t="shared" ref="O5:R8" si="6">$G5/J5</f>
+        <v>-476.02932801822374</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="6"/>
-        <v>148.78990905610664</v>
+        <v>115.6769030577077</v>
       </c>
       <c r="Q5" s="14">
         <f t="shared" si="6"/>
-        <v>106.20637905891151</v>
+        <v>73.975948558427163</v>
       </c>
       <c r="R5" s="14">
         <f t="shared" si="6"/>
-        <v>84.160669704896449</v>
+        <v>60.23974583547637</v>
       </c>
       <c r="S5" s="21">
-        <f>G5/[2]Model!$Q$65</f>
-        <v>12.126442271245548</v>
+        <f>G5/[2]Model!$R$65</f>
+        <v>9.5060784224532036</v>
       </c>
       <c r="T5" s="15">
-        <f>[2]Model!$Q$65/G5-1</f>
-        <v>-0.91753558235532784</v>
+        <f>[2]Model!$R$65/G5-1</f>
+        <v>-0.89480414998070956</v>
       </c>
       <c r="U5" s="15">
         <f>AVERAGE(T5,AC5)</f>
-        <v>-0.85140914199130457</v>
+        <v>-0.77452233232223899</v>
       </c>
       <c r="V5" s="13">
-        <f>[2]Model!$Y$7</f>
-        <v>1976.9399999999998</v>
+        <f>[2]Model!$AC$7</f>
+        <v>2024.1000000000001</v>
       </c>
       <c r="W5" s="23">
-        <f t="shared" ref="W5:W8" si="7">G5/V5</f>
-        <v>16.182575090796888</v>
+        <f t="shared" ref="W5:W9" si="7">G5/V5</f>
+        <v>20.648868632972679</v>
       </c>
       <c r="X5" s="15">
-        <f>[2]Model!X$36</f>
+        <f>[2]Model!AB$36</f>
         <v>0.10537763444086101</v>
       </c>
       <c r="Y5" s="15">
-        <f>[2]Model!Y$36</f>
-        <v>0.34138960510245608</v>
+        <f>[2]Model!AC$36</f>
+        <v>0.37338851947347007</v>
       </c>
       <c r="Z5" s="15">
-        <f>[2]Model!$Y$41</f>
-        <v>0.31610691270347108</v>
+        <f>[2]Model!$AC$41</f>
+        <v>0.29030186255619789</v>
       </c>
       <c r="AA5" s="15">
-        <f>[2]Model!$Y$45</f>
-        <v>4.4829079284146284E-2</v>
+        <f>[2]Model!$AC$45</f>
+        <v>3.6016007114273052E-2</v>
       </c>
       <c r="AB5" s="15">
-        <f>[2]Model!$AM$34</f>
-        <v>0.09</v>
+        <f>[2]Model!$AQ$34</f>
+        <v>0.08</v>
       </c>
       <c r="AC5" s="15">
-        <f>[2]Model!$AM$40</f>
-        <v>-0.7852827016272812</v>
+        <f>[2]Model!$AQ$40</f>
+        <v>-0.65424051466376831</v>
       </c>
       <c r="AD5" s="10" t="str">
-        <f>[2]Model!$AM$41</f>
+        <f>[2]Model!$AQ$41</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AE5" s="10">
@@ -1605,11 +1731,11 @@
       </c>
       <c r="AG5" s="17">
         <f>[2]Main!$E$3</f>
-        <v>45959</v>
+        <v>46076</v>
       </c>
       <c r="AH5" s="17">
         <f>[2]Main!$G$3</f>
-        <v>46058</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="6" spans="2:34" x14ac:dyDescent="0.3">
@@ -1621,19 +1747,19 @@
       </c>
       <c r="D6" s="12">
         <f>[3]Main!$D$3</f>
-        <v>139.09</v>
+        <v>63.83</v>
       </c>
       <c r="E6" s="13">
         <f>[3]Main!$D$5</f>
-        <v>20529.684000000001</v>
+        <v>9970.2459999999992</v>
       </c>
       <c r="F6" s="13">
         <f>[3]Main!$D$8</f>
-        <v>683</v>
+        <v>1183.5999999999999</v>
       </c>
       <c r="G6" s="13">
         <f>[3]Main!$D$9</f>
-        <v>19846.684000000001</v>
+        <v>8786.6459999999988</v>
       </c>
       <c r="H6" s="13">
         <f>[3]Model!Q$17</f>
@@ -1661,35 +1787,35 @@
       </c>
       <c r="N6" s="14">
         <f>$G6/I6</f>
-        <v>-269.29014925373139</v>
+        <v>-119.22179104477613</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="6"/>
-        <v>-177.83767025089608</v>
+        <v>-78.73338709677418</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="6"/>
-        <v>-150.81066869300912</v>
+        <v>-66.767826747720363</v>
       </c>
       <c r="Q6" s="14">
         <f t="shared" si="6"/>
-        <v>-213.81904761904764</v>
+        <v>-94.66328377504847</v>
       </c>
       <c r="R6" s="14">
         <f t="shared" si="6"/>
-        <v>-596.26510440138179</v>
+        <v>-263.98215412347895</v>
       </c>
       <c r="S6" s="21">
         <f>[3]Model!$L$55</f>
-        <v>27.150046511627909</v>
+        <v>12.020035567715457</v>
       </c>
       <c r="T6" s="15">
         <f>[3]Model!$L$56</f>
-        <v>-0.9631676505757838</v>
+        <v>-0.91680557063525714</v>
       </c>
       <c r="U6" s="15">
         <f>AVERAGE(T6,AC6)</f>
-        <v>-0.91857893270577462</v>
+        <v>-0.80356502753664594</v>
       </c>
       <c r="V6" s="18">
         <f>[3]Model!$Q$6</f>
@@ -1718,7 +1844,7 @@
       </c>
       <c r="AC6" s="15">
         <f>[3]Model!$AG$29</f>
-        <v>-0.87399021483576544</v>
+        <v>-0.69032448443803462</v>
       </c>
       <c r="AD6" s="15" t="str">
         <f>[3]Model!$AG$30</f>
@@ -1729,282 +1855,409 @@
       </c>
       <c r="AG6" s="16">
         <f>[3]Main!$E$3</f>
-        <v>45939</v>
+        <v>46076</v>
       </c>
       <c r="AH6" s="16">
         <f>[3]Main!$G$3</f>
-        <v>45988</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D7" s="12">
         <f>[4]Main!$D$3</f>
-        <v>2.46</v>
+        <v>49.74</v>
       </c>
       <c r="E7" s="13">
         <f>[4]Main!$D$5</f>
-        <v>3422.8440000000001</v>
+        <v>6510.9660000000003</v>
       </c>
       <c r="F7" s="13">
         <f>[4]Main!$D$8</f>
-        <v>215.39999999999998</v>
+        <v>274.30000000000018</v>
       </c>
       <c r="G7" s="13">
         <f>[4]Main!$D$9</f>
-        <v>3207.444</v>
+        <v>6236.6660000000002</v>
       </c>
       <c r="H7" s="13">
-        <f>[4]Model!Z$33</f>
-        <v>-1368.8</v>
+        <f>[4]Model!T$18</f>
+        <v>438.99999999999994</v>
       </c>
       <c r="I7" s="13">
-        <f>[4]Model!AA$33</f>
-        <v>-2104.9</v>
+        <f>[4]Model!U$18</f>
+        <v>102.69999999999995</v>
       </c>
       <c r="J7" s="13">
-        <f>[4]Model!AB$33</f>
-        <v>-1049.8714999999997</v>
+        <f>[4]Model!V$18</f>
+        <v>172.09999999999991</v>
       </c>
       <c r="K7" s="13">
-        <f>[4]Model!AC$33</f>
-        <v>-504.67788450000006</v>
+        <f>[4]Model!W$18</f>
+        <v>227.48592500000004</v>
       </c>
       <c r="L7" s="13">
-        <f>[4]Model!AD$33</f>
-        <v>-346.54102523999978</v>
+        <f>[4]Model!X$18</f>
+        <v>242.79734049999996</v>
       </c>
       <c r="M7" s="13">
-        <f>[4]Model!AE$33</f>
-        <v>-189.44181374939978</v>
+        <f>[4]Model!Y$18</f>
+        <v>254.01334320499996</v>
       </c>
       <c r="N7" s="14">
-        <f>$G7/I7</f>
-        <v>-1.5237987552852865</v>
+        <f t="shared" ref="N7" si="8">$G7/I7</f>
+        <v>60.727030185004899</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="6"/>
-        <v>-3.0550824553290576</v>
+        <v>36.238617083091249</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="6"/>
-        <v>-6.3554280829597154</v>
+        <v>27.415612636254306</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="6"/>
-        <v>-9.2555967876491927</v>
+        <v>25.686714636810454</v>
       </c>
       <c r="R7" s="14">
         <f t="shared" si="6"/>
-        <v>-16.931024553232575</v>
-      </c>
-      <c r="S7" s="21">
-        <f>G7/[4]Model!$P$93</f>
-        <v>0.95636114258453087</v>
-      </c>
-      <c r="T7" s="15">
-        <f>[4]Model!$P$93/G7-1</f>
-        <v>4.563010297295933E-2</v>
-      </c>
-      <c r="U7" s="15">
-        <f>AVERAGE(T7,AC7)</f>
-        <v>-0.45911046047068427</v>
-      </c>
-      <c r="V7" s="13">
-        <f>[4]Model!$AB$8</f>
-        <v>722.06</v>
+        <v>24.552513349531942</v>
+      </c>
+      <c r="S7" s="21"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="20">
+        <f>[4]Model!$V$3</f>
+        <v>1473</v>
       </c>
       <c r="W7" s="23">
         <f t="shared" si="7"/>
-        <v>4.4420740658671027</v>
+        <v>4.2339891378139853</v>
       </c>
       <c r="X7" s="15">
-        <f>[4]Model!AA$42</f>
-        <v>-0.29443447037701986</v>
+        <f>[4]Model!U$22</f>
+        <v>-0.41924218613584774</v>
       </c>
       <c r="Y7" s="15">
-        <f>[4]Model!AB$42</f>
-        <v>0.14831424936386761</v>
+        <f>[4]Model!V$22</f>
+        <v>0.1071858087793145</v>
       </c>
       <c r="Z7" s="15">
-        <f>[4]Model!$AB$48</f>
-        <v>-0.49127150098329775</v>
+        <f>[4]Model!$V$23</f>
+        <v>0.4663951120162933</v>
       </c>
       <c r="AA7" s="15">
-        <f>[4]Model!$AB$51</f>
-        <v>-1.3056691964656677</v>
+        <f>[4]Model!$V$27</f>
+        <v>0.10692464358452131</v>
       </c>
       <c r="AB7" s="15">
-        <f>[4]Model!$AP$39</f>
-        <v>0.1</v>
+        <f>[4]Model!$AI$24</f>
+        <v>0.09</v>
       </c>
       <c r="AC7" s="15">
-        <f>[4]Model!$AP$45</f>
-        <v>-0.96385102391432786</v>
-      </c>
-      <c r="AD7" s="10" t="str">
-        <f>[4]Model!$AP$46</f>
+        <f>[4]Model!$AI$30</f>
+        <v>-0.50227926621940466</v>
+      </c>
+      <c r="AD7" s="15" t="str">
+        <f>[4]Model!$AI$31</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AE7" s="10">
-        <v>1997</v>
-      </c>
-      <c r="AG7" s="17">
+        <v>2006</v>
+      </c>
+      <c r="AG7" s="16">
         <f>[4]Main!$E$3</f>
-        <v>45975</v>
-      </c>
-      <c r="AH7" s="17">
+        <v>46078</v>
+      </c>
+      <c r="AH7" s="16">
         <f>[4]Main!$G$3</f>
-        <v>46079</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D8" s="12">
         <f>[5]Main!$D$3</f>
-        <v>8.34</v>
+        <v>1.87</v>
       </c>
       <c r="E8" s="13">
         <f>[5]Main!$D$5</f>
-        <v>397.81800000000004</v>
+        <v>2601.9180000000001</v>
       </c>
       <c r="F8" s="13">
         <f>[5]Main!$D$8</f>
-        <v>210.80000000000007</v>
+        <v>215.39999999999998</v>
       </c>
       <c r="G8" s="13">
         <f>[5]Main!$D$9</f>
-        <v>187.01799999999997</v>
+        <v>2386.518</v>
       </c>
       <c r="H8" s="13">
-        <f>[5]Model!AC$24</f>
-        <v>45.7</v>
+        <f>[5]Model!Z$33</f>
+        <v>-1368.8</v>
       </c>
       <c r="I8" s="13">
-        <f>[5]Model!AD$24</f>
-        <v>31.400000000000002</v>
+        <f>[5]Model!AA$33</f>
+        <v>-2104.9</v>
       </c>
       <c r="J8" s="13">
-        <f>[5]Model!AE$24</f>
-        <v>49.3</v>
+        <f>[5]Model!AB$33</f>
+        <v>-1049.8714999999997</v>
       </c>
       <c r="K8" s="13">
-        <f>[5]Model!AF$24</f>
-        <v>114.3</v>
+        <f>[5]Model!AC$33</f>
+        <v>-504.67788450000006</v>
       </c>
       <c r="L8" s="13">
-        <f>[5]Model!AG$24</f>
-        <v>125.6</v>
+        <f>[5]Model!AD$33</f>
+        <v>-346.54102523999978</v>
       </c>
       <c r="M8" s="13">
-        <f>[5]Model!AH$24</f>
-        <v>122.6</v>
+        <f>[5]Model!AE$33</f>
+        <v>-189.44181374939978</v>
       </c>
       <c r="N8" s="14">
-        <f t="shared" ref="N8" si="8">$G8/I8</f>
-        <v>5.9559872611464959</v>
+        <f>$G8/I8</f>
+        <v>-1.1337916290560122</v>
       </c>
       <c r="O8" s="14">
-        <f t="shared" ref="O8" si="9">$G8/J8</f>
-        <v>3.793468559837728</v>
+        <f t="shared" si="6"/>
+        <v>-2.2731524762792406</v>
       </c>
       <c r="P8" s="14">
-        <f t="shared" ref="P8" si="10">$G8/K8</f>
-        <v>1.6362029746281712</v>
+        <f t="shared" si="6"/>
+        <v>-4.7287944910928621</v>
       </c>
       <c r="Q8" s="14">
-        <f t="shared" ref="Q8" si="11">$G8/L8</f>
-        <v>1.488996815286624</v>
+        <f t="shared" si="6"/>
+        <v>-6.8866824594496361</v>
       </c>
       <c r="R8" s="14">
-        <f t="shared" ref="R8" si="12">$G8/M8</f>
-        <v>1.525432300163132</v>
+        <f t="shared" si="6"/>
+        <v>-12.597630653795202</v>
       </c>
       <c r="S8" s="21">
-        <f>G8/[5]Model!$AI$85</f>
-        <v>0.22516012521069104</v>
+        <f>G8/[5]Model!$P$93</f>
+        <v>0.71158626036138106</v>
       </c>
       <c r="T8" s="15">
-        <f>[5]Model!$AI$85/G8-1</f>
-        <v>3.4412837267001049</v>
+        <f>[5]Model!$P$93/G8-1</f>
+        <v>0.4053110012159975</v>
       </c>
       <c r="U8" s="15">
         <f>AVERAGE(T8,AC8)</f>
-        <v>1.6658810404572626</v>
-      </c>
-      <c r="V8" s="20">
-        <f>[5]Model!$AI$13</f>
-        <v>158</v>
+        <v>-0.24517889097171391</v>
+      </c>
+      <c r="V8" s="13">
+        <f>[5]Model!$AB$8</f>
+        <v>722.06</v>
       </c>
       <c r="W8" s="23">
         <f t="shared" si="7"/>
-        <v>1.1836582278481012</v>
+        <v>3.3051519264327065</v>
       </c>
       <c r="X8" s="15">
-        <f>[5]Model!$AH$45</f>
-        <v>-9.0761750405186525E-2</v>
+        <f>[5]Model!AA$42</f>
+        <v>-0.29443447037701986</v>
       </c>
       <c r="Y8" s="15">
-        <f>[5]Model!$AI$45</f>
-        <v>0.40819964349376114</v>
+        <f>[5]Model!AB$42</f>
+        <v>0.14831424936386761</v>
       </c>
       <c r="Z8" s="15">
-        <f>[5]Model!$AI$50</f>
-        <v>-0.16835443037974679</v>
+        <f>[5]Model!$AB$48</f>
+        <v>-0.49127150098329775</v>
       </c>
       <c r="AA8" s="15">
-        <f>[5]Model!$AI$53</f>
-        <v>-1.218987341772152</v>
+        <f>[5]Model!$AB$51</f>
+        <v>-1.3056691964656677</v>
       </c>
       <c r="AB8" s="15">
-        <f>[5]Model!$AW$43</f>
-        <v>0.12</v>
+        <f>[5]Model!$AP$39</f>
+        <v>0.09</v>
       </c>
       <c r="AC8" s="15">
-        <f>[5]Model!$AW$129</f>
-        <v>-0.10952164578557977</v>
+        <f>[5]Model!$AP$45</f>
+        <v>-0.89566878315942533</v>
       </c>
       <c r="AD8" s="10" t="str">
-        <f>[5]Model!$AW$130</f>
-        <v>Fairly valued</v>
+        <f>[5]Model!$AP$46</f>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AE8" s="10">
-        <v>1969</v>
-      </c>
-      <c r="AG8" s="16">
+        <v>1997</v>
+      </c>
+      <c r="AG8" s="17">
         <f>[5]Main!$E$3</f>
-        <v>46012</v>
-      </c>
-      <c r="AH8" s="16">
+        <v>46076</v>
+      </c>
+      <c r="AH8" s="17">
         <f>[5]Main!$G$3</f>
-        <v>46091</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="B9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="12">
+        <f>[6]Main!$D$3</f>
+        <v>8.34</v>
+      </c>
+      <c r="E9" s="13">
+        <f>[6]Main!$D$5</f>
+        <v>397.81800000000004</v>
+      </c>
+      <c r="F9" s="13">
+        <f>[6]Main!$D$8</f>
+        <v>210.80000000000007</v>
+      </c>
+      <c r="G9" s="13">
+        <f>[6]Main!$D$9</f>
+        <v>187.01799999999997</v>
+      </c>
+      <c r="H9" s="13">
+        <f>[6]Model!AC$24</f>
+        <v>45.7</v>
+      </c>
+      <c r="I9" s="13">
+        <f>[6]Model!AD$24</f>
+        <v>31.400000000000002</v>
+      </c>
+      <c r="J9" s="13">
+        <f>[6]Model!AE$24</f>
+        <v>49.3</v>
+      </c>
+      <c r="K9" s="13">
+        <f>[6]Model!AF$24</f>
+        <v>114.3</v>
+      </c>
+      <c r="L9" s="13">
+        <f>[6]Model!AG$24</f>
+        <v>125.6</v>
+      </c>
+      <c r="M9" s="13">
+        <f>[6]Model!AH$24</f>
+        <v>122.6</v>
+      </c>
+      <c r="N9" s="14">
+        <f t="shared" ref="N9" si="9">$G9/I9</f>
+        <v>5.9559872611464959</v>
+      </c>
+      <c r="O9" s="14">
+        <f t="shared" ref="O9" si="10">$G9/J9</f>
+        <v>3.793468559837728</v>
+      </c>
+      <c r="P9" s="14">
+        <f t="shared" ref="P9" si="11">$G9/K9</f>
+        <v>1.6362029746281712</v>
+      </c>
+      <c r="Q9" s="14">
+        <f t="shared" ref="Q9" si="12">$G9/L9</f>
+        <v>1.488996815286624</v>
+      </c>
+      <c r="R9" s="14">
+        <f t="shared" ref="R9" si="13">$G9/M9</f>
+        <v>1.525432300163132</v>
+      </c>
+      <c r="S9" s="21">
+        <f>G9/[6]Model!$AI$85</f>
+        <v>0.22516012521069104</v>
+      </c>
+      <c r="T9" s="15">
+        <f>[6]Model!$AI$85/G9-1</f>
+        <v>3.4412837267001049</v>
+      </c>
+      <c r="U9" s="15">
+        <f>AVERAGE(T9,AC9)</f>
+        <v>1.8468856683901671</v>
+      </c>
+      <c r="V9" s="20">
+        <f>[6]Model!$AI$13</f>
+        <v>158</v>
+      </c>
+      <c r="W9" s="23">
+        <f t="shared" si="7"/>
+        <v>1.1836582278481012</v>
+      </c>
+      <c r="X9" s="15">
+        <f>[6]Model!$AH$45</f>
+        <v>-9.0761750405186525E-2</v>
+      </c>
+      <c r="Y9" s="15">
+        <f>[6]Model!$AI$45</f>
+        <v>0.40819964349376114</v>
+      </c>
+      <c r="Z9" s="15">
+        <f>[6]Model!$AI$50</f>
+        <v>-0.16835443037974679</v>
+      </c>
+      <c r="AA9" s="15">
+        <f>[6]Model!$AI$53</f>
+        <v>-1.218987341772152</v>
+      </c>
+      <c r="AB9" s="15">
+        <f>[6]Model!$AW$43</f>
+        <v>0.12</v>
+      </c>
+      <c r="AC9" s="15">
+        <f>[6]Model!$AW$129</f>
+        <v>0.25248761008022935</v>
+      </c>
+      <c r="AD9" s="10" t="str">
+        <f>[6]Model!$AW$130</f>
+        <v>Slightly undervalued</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>1969</v>
+      </c>
+      <c r="AG9" s="16">
+        <f>[6]Main!$E$3</f>
+        <v>46012</v>
+      </c>
+      <c r="AH9" s="16">
+        <f>[6]Main!$G$3</f>
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="10" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C10" s="10" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{A639A081-823D-480C-B8E3-E8540E353F47}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{1E28E457-F855-40C5-9070-8BE0C79C6684}"/>
-    <hyperlink ref="B8" r:id="rId3" xr:uid="{A73CB0F7-E51A-47D4-B42C-E9E12E13F561}"/>
+    <hyperlink ref="B9" r:id="rId3" xr:uid="{A73CB0F7-E51A-47D4-B42C-E9E12E13F561}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{1C1D4293-4095-4A0E-A38F-07FACA5B80F2}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{229D4175-EC51-46EF-B3C5-E9711257CB8D}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{229D4175-EC51-46EF-B3C5-E9711257CB8D}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{DFFAF750-74A6-4D62-847F-E0DA365AFC6B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
